--- a/gex_pivot_levels_2026-10-22.xlsx
+++ b/gex_pivot_levels_2026-10-22.xlsx
@@ -15,12 +15,12 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All Pivots" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ES'!$A$1:$G$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ES'!$A$1:$G$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'NQ'!$A$1:$G$39</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'RTY'!$A$1:$G$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'CL'!$A$1:$G$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'GC'!$A$1:$G$21</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'All Pivots'!$A$1:$H$98</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'All Pivots'!$A$1:$H$96</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -109,10 +109,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -544,12 +544,12 @@
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>-$12.86M</t>
+          <t>-$14.92M</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>+$14.46M</t>
+          <t>+$16.77M</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
@@ -577,12 +577,12 @@
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>-$9.29M</t>
+          <t>-$10.27M</t>
         </is>
       </c>
       <c r="E3" s="6" t="inlineStr">
         <is>
-          <t>+$19.76M</t>
+          <t>+$21.84M</t>
         </is>
       </c>
       <c r="F3" s="6" t="inlineStr">
@@ -606,12 +606,12 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>-$865.70K</t>
+          <t>-$952.27K</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>+$12.10M</t>
+          <t>+$13.31M</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
@@ -639,12 +639,12 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>-$18.50M</t>
+          <t>-$19.97M</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>+$20.93M</t>
+          <t>+$22.59M</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
@@ -672,12 +672,12 @@
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>-$7.74M</t>
+          <t>-$8.22M</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>+$9.25M</t>
+          <t>+$9.82M</t>
         </is>
       </c>
       <c r="F6" s="6" t="inlineStr">
@@ -692,252 +692,252 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
+      <c r="A7" s="5" t="n">
+        <v>7672.82</v>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>765</v>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>-$6.18M</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>+$22.27M</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
         <v>7681.83</v>
       </c>
-      <c r="B7" s="2" t="n">
+      <c r="B8" s="2" t="n">
         <v>7685</v>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>SPX</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>-$24.28M</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>+$25.53M</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>-$24.63M</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>+$25.90M</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="G8" s="3" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="5" t="n">
+    <row r="9">
+      <c r="A9" s="5" t="n">
         <v>7686.83</v>
       </c>
-      <c r="B8" s="5" t="n">
+      <c r="B9" s="5" t="n">
         <v>7690</v>
       </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C9" s="6" t="inlineStr">
         <is>
           <t>SPX</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="D9" s="7" t="inlineStr">
         <is>
           <t>-$8.81M</t>
         </is>
       </c>
-      <c r="E8" s="6" t="inlineStr">
+      <c r="E9" s="6" t="inlineStr">
         <is>
           <t>+$11.21M</t>
         </is>
       </c>
-      <c r="F8" s="6" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="G8" s="6" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="n">
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
         <v>7696.83</v>
       </c>
-      <c r="B9" s="2" t="n">
+      <c r="B10" s="2" t="n">
         <v>7700</v>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>SPX</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>-$29.09M</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>+$46.41M</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>-$27.86M</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>+$44.45M</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="G10" s="3" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="5" t="n">
+    <row r="11">
+      <c r="A11" s="5" t="n">
+        <v>7702.93</v>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>768</v>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>-$16.61M</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>+$25.48M</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="n">
         <v>7711.83</v>
       </c>
-      <c r="B10" s="5" t="n">
+      <c r="B12" s="5" t="n">
         <v>7715</v>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C12" s="6" t="inlineStr">
         <is>
           <t>SPX</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
-        <is>
-          <t>-$3.19M</t>
-        </is>
-      </c>
-      <c r="E10" s="6" t="inlineStr">
-        <is>
-          <t>+$8.57M</t>
-        </is>
-      </c>
-      <c r="F10" s="6" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="G10" s="6" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="n">
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>-$2.82M</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>+$7.56M</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
         <v>7716.83</v>
       </c>
-      <c r="B11" s="2" t="n">
+      <c r="B13" s="2" t="n">
         <v>7720</v>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>SPX</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>-$13.88M</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>+$18.35M</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>-$11.99M</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>+$15.85M</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="G13" s="3" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="n">
-        <v>7722.99</v>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>770</v>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>SPY</t>
-        </is>
-      </c>
-      <c r="D12" s="8" t="inlineStr">
-        <is>
-          <t>+$9.52M</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>+$26.42M</t>
-        </is>
-      </c>
-      <c r="F12" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="G12" s="3" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="n">
-        <v>7736.83</v>
-      </c>
-      <c r="B13" s="5" t="n">
-        <v>7740</v>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>SPX</t>
-        </is>
-      </c>
-      <c r="D13" s="7" t="inlineStr">
-        <is>
-          <t>-$1.09M</t>
-        </is>
-      </c>
-      <c r="E13" s="6" t="inlineStr">
-        <is>
-          <t>+$12.90M</t>
-        </is>
-      </c>
-      <c r="F13" s="6" t="inlineStr">
-        <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="G13" s="6" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="n">
-        <v>7743.06</v>
+        <v>7733.03</v>
       </c>
       <c r="B14" s="5" t="n">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
           <t>SPY</t>
         </is>
       </c>
-      <c r="D14" s="7" t="inlineStr">
-        <is>
-          <t>-$4.96M</t>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>+$7.20M</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>+$22.80M</t>
+          <t>+$64.13M</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
@@ -947,30 +947,30 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>valley</t>
+          <t>peak</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="n">
-        <v>7746.83</v>
+        <v>7736.83</v>
       </c>
       <c r="B15" s="5" t="n">
-        <v>7750</v>
+        <v>7740</v>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
           <t>SPX</t>
         </is>
       </c>
-      <c r="D15" s="9" t="inlineStr">
-        <is>
-          <t>+$3.55M</t>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>-$858.72K</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>+$22.44M</t>
+          <t>+$10.17M</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
@@ -982,24 +982,24 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>7773.16</v>
+        <v>7743.06</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>775</v>
+        <v>772</v>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
           <t>SPY</t>
         </is>
       </c>
-      <c r="D16" s="8" t="inlineStr">
-        <is>
-          <t>+$30.11M</t>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>-$21.73M</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>+$45.68M</t>
+          <t>+$70.55M</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
@@ -1009,177 +1009,103 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>peak</t>
+          <t>valley</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="n">
-        <v>7781.83</v>
-      </c>
-      <c r="B17" s="2" t="n">
-        <v>7785</v>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="A17" s="5" t="n">
+        <v>7746.83</v>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>7750</v>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
         <is>
           <t>SPX</t>
         </is>
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t>+$7.40M</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="inlineStr">
-        <is>
-          <t>+$8.28M</t>
-        </is>
-      </c>
-      <c r="F17" s="3" t="inlineStr">
+          <t>+$2.66M</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>+$16.83M</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>7783.2</v>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>776</v>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="inlineStr">
+        <is>
+          <t>+$85.93M</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>+$98.05M</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="G17" s="3" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="5" t="n">
-        <v>7791.83</v>
-      </c>
-      <c r="B18" s="5" t="n">
-        <v>7795</v>
-      </c>
-      <c r="C18" s="6" t="inlineStr">
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="n">
+        <v>7796.83</v>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>7800</v>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
         <is>
           <t>SPX</t>
         </is>
       </c>
-      <c r="D18" s="9" t="inlineStr">
-        <is>
-          <t>+$1.67M</t>
-        </is>
-      </c>
-      <c r="E18" s="6" t="inlineStr">
-        <is>
-          <t>+$1.85M</t>
-        </is>
-      </c>
-      <c r="F18" s="6" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="G18" s="6" t="inlineStr">
-        <is>
-          <t>valley</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="n">
-        <v>7796.83</v>
-      </c>
-      <c r="B19" s="2" t="n">
-        <v>7800</v>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>SPX</t>
-        </is>
-      </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>+$7.34M</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="inlineStr">
-        <is>
-          <t>+$10.81M</t>
-        </is>
-      </c>
-      <c r="F19" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="G19" s="3" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="5" t="n">
-        <v>7813.3</v>
-      </c>
-      <c r="B20" s="5" t="n">
-        <v>779</v>
-      </c>
-      <c r="C20" s="6" t="inlineStr">
-        <is>
-          <t>SPY</t>
-        </is>
-      </c>
-      <c r="D20" s="9" t="inlineStr">
-        <is>
-          <t>+$3.40M</t>
-        </is>
-      </c>
-      <c r="E20" s="6" t="inlineStr">
-        <is>
-          <t>+$8.31M</t>
-        </is>
-      </c>
-      <c r="F20" s="6" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="G20" s="6" t="inlineStr">
-        <is>
-          <t>valley</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="n">
-        <v>7823.33</v>
-      </c>
-      <c r="B21" s="2" t="n">
-        <v>780</v>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>SPY</t>
-        </is>
-      </c>
-      <c r="D21" s="8" t="inlineStr">
-        <is>
-          <t>+$17.95M</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="inlineStr">
-        <is>
-          <t>+$18.14M</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="G21" s="3" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
+          <t>+$4.28M</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>+$6.30M</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G21"/>
+  <autoFilter ref="A1:G19"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1438,7 +1364,7 @@
           <t>QQQ</t>
         </is>
       </c>
-      <c r="D8" s="8" t="inlineStr">
+      <c r="D8" s="9" t="inlineStr">
         <is>
           <t>+$36.56M</t>
         </is>
@@ -1504,7 +1430,7 @@
           <t>NDX</t>
         </is>
       </c>
-      <c r="D10" s="9" t="inlineStr">
+      <c r="D10" s="8" t="inlineStr">
         <is>
           <t>+$11.93K</t>
         </is>
@@ -1628,7 +1554,7 @@
           <t>QQQ</t>
         </is>
       </c>
-      <c r="D14" s="9" t="inlineStr">
+      <c r="D14" s="8" t="inlineStr">
         <is>
           <t>+$425.18K</t>
         </is>
@@ -1727,7 +1653,7 @@
           <t>NDX</t>
         </is>
       </c>
-      <c r="D17" s="9" t="inlineStr">
+      <c r="D17" s="8" t="inlineStr">
         <is>
           <t>+$127.94K</t>
         </is>
@@ -1756,7 +1682,7 @@
           <t>NDX</t>
         </is>
       </c>
-      <c r="D18" s="9" t="inlineStr">
+      <c r="D18" s="8" t="inlineStr">
         <is>
           <t>+$134.50K</t>
         </is>
@@ -1822,7 +1748,7 @@
           <t>NDX</t>
         </is>
       </c>
-      <c r="D20" s="9" t="inlineStr">
+      <c r="D20" s="8" t="inlineStr">
         <is>
           <t>+$49.21K</t>
         </is>
@@ -1888,7 +1814,7 @@
           <t>NDX</t>
         </is>
       </c>
-      <c r="D22" s="8" t="inlineStr">
+      <c r="D22" s="9" t="inlineStr">
         <is>
           <t>+$82.01K</t>
         </is>
@@ -1954,7 +1880,7 @@
           <t>NDX</t>
         </is>
       </c>
-      <c r="D24" s="9" t="inlineStr">
+      <c r="D24" s="8" t="inlineStr">
         <is>
           <t>+$45.93K</t>
         </is>
@@ -2020,7 +1946,7 @@
           <t>QQQ</t>
         </is>
       </c>
-      <c r="D26" s="8" t="inlineStr">
+      <c r="D26" s="9" t="inlineStr">
         <is>
           <t>+$8.85M</t>
         </is>
@@ -2053,7 +1979,7 @@
           <t>NDX</t>
         </is>
       </c>
-      <c r="D27" s="8" t="inlineStr">
+      <c r="D27" s="9" t="inlineStr">
         <is>
           <t>+$98.41K</t>
         </is>
@@ -2086,7 +2012,7 @@
           <t>NDX</t>
         </is>
       </c>
-      <c r="D28" s="9" t="inlineStr">
+      <c r="D28" s="8" t="inlineStr">
         <is>
           <t>+$11.93K</t>
         </is>
@@ -2119,7 +2045,7 @@
           <t>NDX</t>
         </is>
       </c>
-      <c r="D29" s="8" t="inlineStr">
+      <c r="D29" s="9" t="inlineStr">
         <is>
           <t>+$74.56K</t>
         </is>
@@ -2152,7 +2078,7 @@
           <t>NDX</t>
         </is>
       </c>
-      <c r="D30" s="9" t="inlineStr">
+      <c r="D30" s="8" t="inlineStr">
         <is>
           <t>+$26.84K</t>
         </is>
@@ -2185,7 +2111,7 @@
           <t>QQQ</t>
         </is>
       </c>
-      <c r="D31" s="9" t="inlineStr">
+      <c r="D31" s="8" t="inlineStr">
         <is>
           <t>+$631.92K</t>
         </is>
@@ -2218,7 +2144,7 @@
           <t>NDX</t>
         </is>
       </c>
-      <c r="D32" s="8" t="inlineStr">
+      <c r="D32" s="9" t="inlineStr">
         <is>
           <t>+$164.02K</t>
         </is>
@@ -2251,7 +2177,7 @@
           <t>NDX</t>
         </is>
       </c>
-      <c r="D33" s="9" t="inlineStr">
+      <c r="D33" s="8" t="inlineStr">
         <is>
           <t>+$32.80K</t>
         </is>
@@ -2284,7 +2210,7 @@
           <t>NDX</t>
         </is>
       </c>
-      <c r="D34" s="8" t="inlineStr">
+      <c r="D34" s="9" t="inlineStr">
         <is>
           <t>+$83.50K</t>
         </is>
@@ -2317,7 +2243,7 @@
           <t>QQQ</t>
         </is>
       </c>
-      <c r="D35" s="8" t="inlineStr">
+      <c r="D35" s="9" t="inlineStr">
         <is>
           <t>+$11.48M</t>
         </is>
@@ -2350,7 +2276,7 @@
           <t>QQQ</t>
         </is>
       </c>
-      <c r="D36" s="9" t="inlineStr">
+      <c r="D36" s="8" t="inlineStr">
         <is>
           <t>+$1.58M</t>
         </is>
@@ -2383,7 +2309,7 @@
           <t>QQQ</t>
         </is>
       </c>
-      <c r="D37" s="8" t="inlineStr">
+      <c r="D37" s="9" t="inlineStr">
         <is>
           <t>+$32.66M</t>
         </is>
@@ -2416,7 +2342,7 @@
           <t>QQQ</t>
         </is>
       </c>
-      <c r="D38" s="9" t="inlineStr">
+      <c r="D38" s="8" t="inlineStr">
         <is>
           <t>+$462.77K</t>
         </is>
@@ -2449,7 +2375,7 @@
           <t>QQQ</t>
         </is>
       </c>
-      <c r="D39" s="8" t="inlineStr">
+      <c r="D39" s="9" t="inlineStr">
         <is>
           <t>+$21.82M</t>
         </is>
@@ -2544,7 +2470,7 @@
           <t>IWM</t>
         </is>
       </c>
-      <c r="D2" s="8" t="inlineStr">
+      <c r="D2" s="9" t="inlineStr">
         <is>
           <t>+$5.37M</t>
         </is>
@@ -2610,7 +2536,7 @@
           <t>IWM</t>
         </is>
       </c>
-      <c r="D4" s="9" t="inlineStr">
+      <c r="D4" s="8" t="inlineStr">
         <is>
           <t>+$4.15M</t>
         </is>
@@ -2639,7 +2565,7 @@
           <t>IWM</t>
         </is>
       </c>
-      <c r="D5" s="8" t="inlineStr">
+      <c r="D5" s="9" t="inlineStr">
         <is>
           <t>+$15.14M</t>
         </is>
@@ -2672,7 +2598,7 @@
           <t>IWM</t>
         </is>
       </c>
-      <c r="D6" s="9" t="inlineStr">
+      <c r="D6" s="8" t="inlineStr">
         <is>
           <t>+$580.02K</t>
         </is>
@@ -2705,7 +2631,7 @@
           <t>IWM</t>
         </is>
       </c>
-      <c r="D7" s="8" t="inlineStr">
+      <c r="D7" s="9" t="inlineStr">
         <is>
           <t>+$5.35M</t>
         </is>
@@ -2887,7 +2813,7 @@
           <t>USO</t>
         </is>
       </c>
-      <c r="D5" s="8" t="inlineStr">
+      <c r="D5" s="9" t="inlineStr">
         <is>
           <t>+$821.39K</t>
         </is>
@@ -2920,7 +2846,7 @@
           <t>USO</t>
         </is>
       </c>
-      <c r="D6" s="9" t="inlineStr">
+      <c r="D6" s="8" t="inlineStr">
         <is>
           <t>+$127.52K</t>
         </is>
@@ -2953,7 +2879,7 @@
           <t>USO</t>
         </is>
       </c>
-      <c r="D7" s="9" t="inlineStr">
+      <c r="D7" s="8" t="inlineStr">
         <is>
           <t>+$1.68M</t>
         </is>
@@ -2982,7 +2908,7 @@
           <t>USO</t>
         </is>
       </c>
-      <c r="D8" s="9" t="inlineStr">
+      <c r="D8" s="8" t="inlineStr">
         <is>
           <t>+$1.74M</t>
         </is>
@@ -3015,7 +2941,7 @@
           <t>USO</t>
         </is>
       </c>
-      <c r="D9" s="9" t="inlineStr">
+      <c r="D9" s="8" t="inlineStr">
         <is>
           <t>+$1.54M</t>
         </is>
@@ -3044,7 +2970,7 @@
           <t>USO</t>
         </is>
       </c>
-      <c r="D10" s="9" t="inlineStr">
+      <c r="D10" s="8" t="inlineStr">
         <is>
           <t>+$230.88K</t>
         </is>
@@ -3077,7 +3003,7 @@
           <t>USO</t>
         </is>
       </c>
-      <c r="D11" s="8" t="inlineStr">
+      <c r="D11" s="9" t="inlineStr">
         <is>
           <t>+$2.93M</t>
         </is>
@@ -3110,7 +3036,7 @@
           <t>USO</t>
         </is>
       </c>
-      <c r="D12" s="9" t="inlineStr">
+      <c r="D12" s="8" t="inlineStr">
         <is>
           <t>+$478.68K</t>
         </is>
@@ -3139,7 +3065,7 @@
           <t>USO</t>
         </is>
       </c>
-      <c r="D13" s="9" t="inlineStr">
+      <c r="D13" s="8" t="inlineStr">
         <is>
           <t>+$116.02K</t>
         </is>
@@ -3172,7 +3098,7 @@
           <t>USO</t>
         </is>
       </c>
-      <c r="D14" s="8" t="inlineStr">
+      <c r="D14" s="9" t="inlineStr">
         <is>
           <t>+$1.03M</t>
         </is>
@@ -3362,7 +3288,7 @@
           <t>GDX</t>
         </is>
       </c>
-      <c r="D5" s="9" t="inlineStr">
+      <c r="D5" s="8" t="inlineStr">
         <is>
           <t>+$3.23M</t>
         </is>
@@ -3428,7 +3354,7 @@
           <t>GLD</t>
         </is>
       </c>
-      <c r="D7" s="9" t="inlineStr">
+      <c r="D7" s="8" t="inlineStr">
         <is>
           <t>+$186.16K</t>
         </is>
@@ -3494,7 +3420,7 @@
           <t>GLD</t>
         </is>
       </c>
-      <c r="D9" s="9" t="inlineStr">
+      <c r="D9" s="8" t="inlineStr">
         <is>
           <t>+$731.57K</t>
         </is>
@@ -3523,7 +3449,7 @@
           <t>GLD</t>
         </is>
       </c>
-      <c r="D10" s="9" t="inlineStr">
+      <c r="D10" s="8" t="inlineStr">
         <is>
           <t>+$969.66K</t>
         </is>
@@ -3556,7 +3482,7 @@
           <t>GLD</t>
         </is>
       </c>
-      <c r="D11" s="9" t="inlineStr">
+      <c r="D11" s="8" t="inlineStr">
         <is>
           <t>+$484.07K</t>
         </is>
@@ -3589,7 +3515,7 @@
           <t>GLD</t>
         </is>
       </c>
-      <c r="D12" s="9" t="inlineStr">
+      <c r="D12" s="8" t="inlineStr">
         <is>
           <t>+$796.41K</t>
         </is>
@@ -3622,7 +3548,7 @@
           <t>GDX</t>
         </is>
       </c>
-      <c r="D13" s="8" t="inlineStr">
+      <c r="D13" s="9" t="inlineStr">
         <is>
           <t>+$10.38M</t>
         </is>
@@ -3655,7 +3581,7 @@
           <t>GDX</t>
         </is>
       </c>
-      <c r="D14" s="9" t="inlineStr">
+      <c r="D14" s="8" t="inlineStr">
         <is>
           <t>+$14.47K</t>
         </is>
@@ -3688,7 +3614,7 @@
           <t>GDX</t>
         </is>
       </c>
-      <c r="D15" s="8" t="inlineStr">
+      <c r="D15" s="9" t="inlineStr">
         <is>
           <t>+$9.41M</t>
         </is>
@@ -3721,7 +3647,7 @@
           <t>GDX</t>
         </is>
       </c>
-      <c r="D16" s="9" t="inlineStr">
+      <c r="D16" s="8" t="inlineStr">
         <is>
           <t>+$37.20K</t>
         </is>
@@ -3754,7 +3680,7 @@
           <t>GDX</t>
         </is>
       </c>
-      <c r="D17" s="8" t="inlineStr">
+      <c r="D17" s="9" t="inlineStr">
         <is>
           <t>+$7.18M</t>
         </is>
@@ -3787,7 +3713,7 @@
           <t>GDX</t>
         </is>
       </c>
-      <c r="D18" s="9" t="inlineStr">
+      <c r="D18" s="8" t="inlineStr">
         <is>
           <t>+$193.31K</t>
         </is>
@@ -3820,7 +3746,7 @@
           <t>GDX</t>
         </is>
       </c>
-      <c r="D19" s="8" t="inlineStr">
+      <c r="D19" s="9" t="inlineStr">
         <is>
           <t>+$3.08M</t>
         </is>
@@ -3853,7 +3779,7 @@
           <t>GDX</t>
         </is>
       </c>
-      <c r="D20" s="9" t="inlineStr">
+      <c r="D20" s="8" t="inlineStr">
         <is>
           <t>+$50.95K</t>
         </is>
@@ -3886,7 +3812,7 @@
           <t>GDX</t>
         </is>
       </c>
-      <c r="D21" s="8" t="inlineStr">
+      <c r="D21" s="9" t="inlineStr">
         <is>
           <t>+$3.25M</t>
         </is>
@@ -3920,7 +3846,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H98"/>
+  <dimension ref="A1:H96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3982,24 +3908,24 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>7696.83</v>
+        <v>7783.2</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>7700</v>
+        <v>776</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>SPX</t>
-        </is>
-      </c>
-      <c r="E2" s="4" t="inlineStr">
-        <is>
-          <t>-$29.09M</t>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="E2" s="9" t="inlineStr">
+        <is>
+          <t>+$85.93M</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>+$46.41M</t>
+          <t>+$98.05M</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
@@ -4009,7 +3935,7 @@
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>valley</t>
+          <t>peak</t>
         </is>
       </c>
     </row>
@@ -4020,24 +3946,24 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>7773.16</v>
+        <v>7743.06</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>775</v>
+        <v>772</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
           <t>SPY</t>
         </is>
       </c>
-      <c r="E3" s="8" t="inlineStr">
-        <is>
-          <t>+$30.11M</t>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>-$21.73M</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>+$45.68M</t>
+          <t>+$70.55M</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
@@ -4047,43 +3973,43 @@
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>peak</t>
+          <t>valley</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>NQ</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="n">
-        <v>29513.91</v>
-      </c>
-      <c r="C4" s="2" t="n">
-        <v>722</v>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>QQQ</t>
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>7733.03</v>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>771</v>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>SPY</t>
         </is>
       </c>
       <c r="E4" s="8" t="inlineStr">
         <is>
-          <t>+$36.56M</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>+$41.54M</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
+          <t>+$7.20M</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>+$64.13M</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
@@ -4092,28 +4018,28 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>NQ</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>29966.26</v>
+        <v>7696.83</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>733</v>
+        <v>7700</v>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>QQQ</t>
-        </is>
-      </c>
-      <c r="E5" s="8" t="inlineStr">
-        <is>
-          <t>+$32.66M</t>
+          <t>SPX</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>-$27.86M</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>+$33.14M</t>
+          <t>+$44.45M</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -4123,35 +4049,35 @@
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>peak</t>
+          <t>valley</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>NQ</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>7722.99</v>
+        <v>29513.91</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>770</v>
+        <v>722</v>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>SPY</t>
-        </is>
-      </c>
-      <c r="E6" s="8" t="inlineStr">
-        <is>
-          <t>+$9.52M</t>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>+$36.56M</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>+$26.42M</t>
+          <t>+$41.54M</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
@@ -4168,74 +4094,74 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>29966.26</v>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>733</v>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="inlineStr">
+        <is>
+          <t>+$32.66M</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>+$33.14M</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="B7" s="2" t="n">
+      <c r="B8" s="2" t="n">
         <v>7681.83</v>
       </c>
-      <c r="C7" s="2" t="n">
+      <c r="C8" s="2" t="n">
         <v>7685</v>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>SPX</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>-$24.28M</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>+$25.53M</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>-$24.63M</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>+$25.90M</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>valley</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="n">
-        <v>7743.06</v>
-      </c>
-      <c r="C8" s="5" t="n">
-        <v>772</v>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>SPY</t>
-        </is>
-      </c>
-      <c r="E8" s="7" t="inlineStr">
-        <is>
-          <t>-$4.96M</t>
-        </is>
-      </c>
-      <c r="F8" s="6" t="inlineStr">
-        <is>
-          <t>+$22.80M</t>
-        </is>
-      </c>
-      <c r="G8" s="6" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H8" s="6" t="inlineStr">
+      <c r="H8" s="3" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
@@ -4248,244 +4174,240 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>7746.83</v>
+        <v>7702.93</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>7750</v>
+        <v>768</v>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>SPX</t>
-        </is>
-      </c>
-      <c r="E9" s="9" t="inlineStr">
-        <is>
-          <t>+$3.55M</t>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>-$16.61M</t>
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>+$22.44M</t>
+          <t>+$25.48M</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H9" s="6" t="inlineStr"/>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>7666.83</v>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>7670</v>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>SPX</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>-$19.97M</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>+$22.59M</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>7672.82</v>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>765</v>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>-$6.18M</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>+$22.27M</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
           <t>NQ</t>
         </is>
       </c>
-      <c r="B10" s="2" t="n">
+      <c r="B12" s="2" t="n">
         <v>30089.63</v>
       </c>
-      <c r="C10" s="2" t="n">
+      <c r="C12" s="2" t="n">
         <v>736</v>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>QQQ</t>
         </is>
       </c>
-      <c r="E10" s="8" t="inlineStr">
+      <c r="E12" s="9" t="inlineStr">
         <is>
           <t>+$21.82M</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="F12" s="3" t="inlineStr">
         <is>
           <t>+$22.00M</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="G12" s="3" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="B11" s="2" t="n">
-        <v>7666.83</v>
-      </c>
-      <c r="C11" s="2" t="n">
-        <v>7670</v>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="B13" s="5" t="n">
+        <v>7656.83</v>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>7660</v>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
         <is>
           <t>SPX</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>-$18.50M</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t>+$20.93M</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t>valley</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>-$10.27M</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>+$21.84M</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="B12" s="5" t="n">
-        <v>7656.83</v>
-      </c>
-      <c r="C12" s="5" t="n">
-        <v>7660</v>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
+      <c r="B14" s="5" t="n">
+        <v>7746.83</v>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>7750</v>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
         <is>
           <t>SPX</t>
         </is>
       </c>
-      <c r="E12" s="7" t="inlineStr">
-        <is>
-          <t>-$9.29M</t>
-        </is>
-      </c>
-      <c r="F12" s="6" t="inlineStr">
-        <is>
-          <t>+$19.76M</t>
-        </is>
-      </c>
-      <c r="G12" s="6" t="inlineStr">
+      <c r="E14" s="8" t="inlineStr">
+        <is>
+          <t>+$2.66M</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>+$16.83M</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="H12" s="6" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n">
-        <v>7716.83</v>
-      </c>
-      <c r="C13" s="2" t="n">
-        <v>7720</v>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>SPX</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>-$13.88M</t>
-        </is>
-      </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t>+$18.35M</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H13" s="3" t="inlineStr">
-        <is>
-          <t>valley</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>7823.33</v>
-      </c>
-      <c r="C14" s="2" t="n">
-        <v>780</v>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>SPY</t>
-        </is>
-      </c>
-      <c r="E14" s="8" t="inlineStr">
-        <is>
-          <t>+$17.95M</t>
-        </is>
-      </c>
-      <c r="F14" s="3" t="inlineStr">
-        <is>
-          <t>+$18.14M</t>
-        </is>
-      </c>
-      <c r="G14" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H14" s="3" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
+      <c r="H14" s="6" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>NQ</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>29842.89</v>
+        <v>7646.83</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>730</v>
+        <v>7650</v>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>QQQ</t>
-        </is>
-      </c>
-      <c r="E15" s="8" t="inlineStr">
-        <is>
-          <t>+$11.48M</t>
+          <t>SPX</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>-$14.92M</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>+$15.56M</t>
+          <t>+$16.77M</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
@@ -4495,35 +4417,35 @@
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>peak</t>
+          <t>valley</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>RTY</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>2816.8</v>
+        <v>7716.83</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>280</v>
+        <v>7720</v>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>IWM</t>
-        </is>
-      </c>
-      <c r="E16" s="8" t="inlineStr">
-        <is>
-          <t>+$15.14M</t>
+          <t>SPX</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>-$11.99M</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>+$15.39M</t>
+          <t>+$15.85M</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
@@ -4533,35 +4455,35 @@
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>peak</t>
+          <t>valley</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>RTY</t>
+          <t>NQ</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>2766.5</v>
+        <v>29842.89</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>275</v>
+        <v>730</v>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>IWM</t>
-        </is>
-      </c>
-      <c r="E17" s="8" t="inlineStr">
-        <is>
-          <t>+$5.37M</t>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="E17" s="9" t="inlineStr">
+        <is>
+          <t>+$11.48M</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>+$14.60M</t>
+          <t>+$15.56M</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
@@ -4578,28 +4500,28 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>RTY</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>7646.83</v>
+        <v>2816.8</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>7650</v>
+        <v>280</v>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>SPX</t>
-        </is>
-      </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>-$12.86M</t>
+          <t>IWM</t>
+        </is>
+      </c>
+      <c r="E18" s="9" t="inlineStr">
+        <is>
+          <t>+$15.14M</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>+$14.46M</t>
+          <t>+$15.39M</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
@@ -4609,43 +4531,47 @@
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>valley</t>
+          <t>peak</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="n">
-        <v>7736.83</v>
-      </c>
-      <c r="C19" s="5" t="n">
-        <v>7740</v>
-      </c>
-      <c r="D19" s="6" t="inlineStr">
-        <is>
-          <t>SPX</t>
-        </is>
-      </c>
-      <c r="E19" s="7" t="inlineStr">
-        <is>
-          <t>-$1.09M</t>
-        </is>
-      </c>
-      <c r="F19" s="6" t="inlineStr">
-        <is>
-          <t>+$12.90M</t>
-        </is>
-      </c>
-      <c r="G19" s="6" t="inlineStr">
-        <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H19" s="6" t="inlineStr"/>
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>RTY</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>2766.5</v>
+      </c>
+      <c r="C19" s="2" t="n">
+        <v>275</v>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>IWM</t>
+        </is>
+      </c>
+      <c r="E19" s="9" t="inlineStr">
+        <is>
+          <t>+$5.37M</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>+$14.60M</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
@@ -4666,12 +4592,12 @@
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>-$865.70K</t>
+          <t>-$952.27K</t>
         </is>
       </c>
       <c r="F20" s="6" t="inlineStr">
         <is>
-          <t>+$12.10M</t>
+          <t>+$13.31M</t>
         </is>
       </c>
       <c r="G20" s="6" t="inlineStr">
@@ -4702,7 +4628,7 @@
           <t>GDX</t>
         </is>
       </c>
-      <c r="E21" s="8" t="inlineStr">
+      <c r="E21" s="9" t="inlineStr">
         <is>
           <t>+$10.38M</t>
         </is>
@@ -4762,42 +4688,38 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="inlineStr">
+      <c r="A23" s="6" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="B23" s="2" t="n">
-        <v>7796.83</v>
-      </c>
-      <c r="C23" s="2" t="n">
-        <v>7800</v>
-      </c>
-      <c r="D23" s="3" t="inlineStr">
+      <c r="B23" s="5" t="n">
+        <v>7736.83</v>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>7740</v>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
         <is>
           <t>SPX</t>
         </is>
       </c>
-      <c r="E23" s="8" t="inlineStr">
-        <is>
-          <t>+$7.34M</t>
-        </is>
-      </c>
-      <c r="F23" s="3" t="inlineStr">
-        <is>
-          <t>+$10.81M</t>
-        </is>
-      </c>
-      <c r="G23" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H23" s="3" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>-$858.72K</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>+$10.17M</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H23" s="6" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
@@ -4816,7 +4738,7 @@
           <t>GDX</t>
         </is>
       </c>
-      <c r="E24" s="8" t="inlineStr">
+      <c r="E24" s="9" t="inlineStr">
         <is>
           <t>+$9.41M</t>
         </is>
@@ -4838,102 +4760,106 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="inlineStr">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>7671.83</v>
+      </c>
+      <c r="C25" s="5" t="n">
+        <v>7675</v>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>SPX</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>-$8.22M</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>+$9.82M</t>
+        </is>
+      </c>
+      <c r="G25" s="6" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H25" s="6" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
         <is>
           <t>NQ</t>
         </is>
       </c>
-      <c r="B25" s="2" t="n">
+      <c r="B26" s="2" t="n">
         <v>29760.64</v>
       </c>
-      <c r="C25" s="2" t="n">
+      <c r="C26" s="2" t="n">
         <v>728</v>
       </c>
-      <c r="D25" s="3" t="inlineStr">
+      <c r="D26" s="3" t="inlineStr">
         <is>
           <t>QQQ</t>
         </is>
       </c>
-      <c r="E25" s="8" t="inlineStr">
+      <c r="E26" s="9" t="inlineStr">
         <is>
           <t>+$8.85M</t>
         </is>
       </c>
-      <c r="F25" s="3" t="inlineStr">
+      <c r="F26" s="3" t="inlineStr">
         <is>
           <t>+$9.79M</t>
         </is>
       </c>
-      <c r="G25" s="3" t="inlineStr">
+      <c r="G26" s="3" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="H25" s="3" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="6" t="inlineStr">
-        <is>
-          <t>NQ</t>
-        </is>
-      </c>
-      <c r="B26" s="5" t="n">
-        <v>29431.66</v>
-      </c>
-      <c r="C26" s="5" t="n">
-        <v>720</v>
-      </c>
-      <c r="D26" s="6" t="inlineStr">
-        <is>
-          <t>QQQ</t>
-        </is>
-      </c>
-      <c r="E26" s="7" t="inlineStr">
-        <is>
-          <t>-$641.02K</t>
-        </is>
-      </c>
-      <c r="F26" s="6" t="inlineStr">
-        <is>
-          <t>+$9.47M</t>
-        </is>
-      </c>
-      <c r="G26" s="6" t="inlineStr">
-        <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H26" s="6" t="inlineStr"/>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>RTY</t>
+          <t>NQ</t>
         </is>
       </c>
       <c r="B27" s="5" t="n">
-        <v>2786.62</v>
+        <v>29431.66</v>
       </c>
       <c r="C27" s="5" t="n">
-        <v>277</v>
+        <v>720</v>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>IWM</t>
-        </is>
-      </c>
-      <c r="E27" s="9" t="inlineStr">
-        <is>
-          <t>+$4.15M</t>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>-$641.02K</t>
         </is>
       </c>
       <c r="F27" s="6" t="inlineStr">
         <is>
-          <t>+$9.27M</t>
+          <t>+$9.47M</t>
         </is>
       </c>
       <c r="G27" s="6" t="inlineStr">
@@ -4946,40 +4872,36 @@
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>RTY</t>
         </is>
       </c>
       <c r="B28" s="5" t="n">
-        <v>7671.83</v>
+        <v>2786.62</v>
       </c>
       <c r="C28" s="5" t="n">
-        <v>7675</v>
+        <v>277</v>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>SPX</t>
-        </is>
-      </c>
-      <c r="E28" s="7" t="inlineStr">
-        <is>
-          <t>-$7.74M</t>
+          <t>IWM</t>
+        </is>
+      </c>
+      <c r="E28" s="8" t="inlineStr">
+        <is>
+          <t>+$4.15M</t>
         </is>
       </c>
       <c r="F28" s="6" t="inlineStr">
         <is>
-          <t>+$9.25M</t>
+          <t>+$9.27M</t>
         </is>
       </c>
       <c r="G28" s="6" t="inlineStr">
         <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H28" s="6" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H28" s="6" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
@@ -4998,7 +4920,7 @@
           <t>GDX</t>
         </is>
       </c>
-      <c r="E29" s="8" t="inlineStr">
+      <c r="E29" s="9" t="inlineStr">
         <is>
           <t>+$7.18M</t>
         </is>
@@ -5020,40 +4942,40 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="6" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="B30" s="5" t="n">
-        <v>7711.83</v>
-      </c>
-      <c r="C30" s="5" t="n">
-        <v>7715</v>
-      </c>
-      <c r="D30" s="6" t="inlineStr">
-        <is>
-          <t>SPX</t>
-        </is>
-      </c>
-      <c r="E30" s="7" t="inlineStr">
-        <is>
-          <t>-$3.19M</t>
-        </is>
-      </c>
-      <c r="F30" s="6" t="inlineStr">
-        <is>
-          <t>+$8.57M</t>
-        </is>
-      </c>
-      <c r="G30" s="6" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H30" s="6" t="inlineStr">
-        <is>
-          <t>peak</t>
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>28938.18</v>
+      </c>
+      <c r="C30" s="2" t="n">
+        <v>708</v>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>-$7.56M</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>+$7.78M</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>valley</t>
         </is>
       </c>
     </row>
@@ -5064,24 +4986,24 @@
         </is>
       </c>
       <c r="B31" s="5" t="n">
-        <v>7813.3</v>
+        <v>7711.83</v>
       </c>
       <c r="C31" s="5" t="n">
-        <v>779</v>
+        <v>7715</v>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>SPY</t>
-        </is>
-      </c>
-      <c r="E31" s="9" t="inlineStr">
-        <is>
-          <t>+$3.40M</t>
+          <t>SPX</t>
+        </is>
+      </c>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>-$2.82M</t>
         </is>
       </c>
       <c r="F31" s="6" t="inlineStr">
         <is>
-          <t>+$8.31M</t>
+          <t>+$7.56M</t>
         </is>
       </c>
       <c r="G31" s="6" t="inlineStr">
@@ -5091,183 +5013,179 @@
       </c>
       <c r="H31" s="6" t="inlineStr">
         <is>
+          <t>peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>RTY</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>2776.56</v>
+      </c>
+      <c r="C32" s="5" t="n">
+        <v>276</v>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>IWM</t>
+        </is>
+      </c>
+      <c r="E32" s="7" t="inlineStr">
+        <is>
+          <t>-$15.19K</t>
+        </is>
+      </c>
+      <c r="F32" s="6" t="inlineStr">
+        <is>
+          <t>+$6.98M</t>
+        </is>
+      </c>
+      <c r="G32" s="6" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H32" s="6" t="inlineStr">
+        <is>
           <t>valley</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="3" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="B32" s="2" t="n">
-        <v>7781.83</v>
-      </c>
-      <c r="C32" s="2" t="n">
-        <v>7785</v>
-      </c>
-      <c r="D32" s="3" t="inlineStr">
+      <c r="B33" s="5" t="n">
+        <v>7796.83</v>
+      </c>
+      <c r="C33" s="5" t="n">
+        <v>7800</v>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
         <is>
           <t>SPX</t>
         </is>
       </c>
-      <c r="E32" s="8" t="inlineStr">
-        <is>
-          <t>+$7.40M</t>
-        </is>
-      </c>
-      <c r="F32" s="3" t="inlineStr">
-        <is>
-          <t>+$8.28M</t>
-        </is>
-      </c>
-      <c r="G32" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H32" s="3" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="3" t="inlineStr">
-        <is>
-          <t>NQ</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="n">
-        <v>28938.18</v>
-      </c>
-      <c r="C33" s="2" t="n">
-        <v>708</v>
-      </c>
-      <c r="D33" s="3" t="inlineStr">
-        <is>
-          <t>QQQ</t>
-        </is>
-      </c>
-      <c r="E33" s="4" t="inlineStr">
-        <is>
-          <t>-$7.56M</t>
-        </is>
-      </c>
-      <c r="F33" s="3" t="inlineStr">
-        <is>
-          <t>+$7.78M</t>
-        </is>
-      </c>
-      <c r="G33" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H33" s="3" t="inlineStr">
-        <is>
-          <t>valley</t>
-        </is>
-      </c>
+      <c r="E33" s="8" t="inlineStr">
+        <is>
+          <t>+$4.28M</t>
+        </is>
+      </c>
+      <c r="F33" s="6" t="inlineStr">
+        <is>
+          <t>+$6.30M</t>
+        </is>
+      </c>
+      <c r="G33" s="6" t="inlineStr">
+        <is>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H33" s="6" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
         <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>29226.04</v>
+      </c>
+      <c r="C34" s="5" t="n">
+        <v>715</v>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="E34" s="7" t="inlineStr">
+        <is>
+          <t>-$3.48M</t>
+        </is>
+      </c>
+      <c r="F34" s="6" t="inlineStr">
+        <is>
+          <t>+$5.36M</t>
+        </is>
+      </c>
+      <c r="G34" s="6" t="inlineStr">
+        <is>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H34" s="6" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
           <t>RTY</t>
         </is>
       </c>
-      <c r="B34" s="5" t="n">
-        <v>2776.56</v>
-      </c>
-      <c r="C34" s="5" t="n">
-        <v>276</v>
-      </c>
-      <c r="D34" s="6" t="inlineStr">
+      <c r="B35" s="2" t="n">
+        <v>2836.92</v>
+      </c>
+      <c r="C35" s="2" t="n">
+        <v>282</v>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
         <is>
           <t>IWM</t>
         </is>
       </c>
-      <c r="E34" s="7" t="inlineStr">
-        <is>
-          <t>-$15.19K</t>
-        </is>
-      </c>
-      <c r="F34" s="6" t="inlineStr">
-        <is>
-          <t>+$6.98M</t>
-        </is>
-      </c>
-      <c r="G34" s="6" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H34" s="6" t="inlineStr">
-        <is>
-          <t>valley</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="6" t="inlineStr">
-        <is>
-          <t>NQ</t>
-        </is>
-      </c>
-      <c r="B35" s="5" t="n">
-        <v>29226.04</v>
-      </c>
-      <c r="C35" s="5" t="n">
-        <v>715</v>
-      </c>
-      <c r="D35" s="6" t="inlineStr">
-        <is>
-          <t>QQQ</t>
-        </is>
-      </c>
-      <c r="E35" s="7" t="inlineStr">
-        <is>
-          <t>-$3.48M</t>
-        </is>
-      </c>
-      <c r="F35" s="6" t="inlineStr">
+      <c r="E35" s="9" t="inlineStr">
+        <is>
+          <t>+$5.35M</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
         <is>
           <t>+$5.36M</t>
         </is>
       </c>
-      <c r="G35" s="6" t="inlineStr">
-        <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H35" s="6" t="inlineStr"/>
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>RTY</t>
+          <t>GC</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
-        <v>2836.92</v>
+        <v>4028.68</v>
       </c>
       <c r="C36" s="2" t="n">
-        <v>282</v>
+        <v>85</v>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>IWM</t>
-        </is>
-      </c>
-      <c r="E36" s="8" t="inlineStr">
-        <is>
-          <t>+$5.35M</t>
+          <t>GDX</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>-$4.97M</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>+$5.36M</t>
+          <t>+$5.31M</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
@@ -5277,43 +5195,43 @@
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>peak</t>
+          <t>valley</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="inlineStr">
-        <is>
-          <t>GC</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="n">
-        <v>4028.68</v>
-      </c>
-      <c r="C37" s="2" t="n">
-        <v>85</v>
-      </c>
-      <c r="D37" s="3" t="inlineStr">
-        <is>
-          <t>GDX</t>
-        </is>
-      </c>
-      <c r="E37" s="4" t="inlineStr">
-        <is>
-          <t>-$4.97M</t>
-        </is>
-      </c>
-      <c r="F37" s="3" t="inlineStr">
-        <is>
-          <t>+$5.31M</t>
-        </is>
-      </c>
-      <c r="G37" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H37" s="3" t="inlineStr">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>29596.15</v>
+      </c>
+      <c r="C37" s="5" t="n">
+        <v>724</v>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="E37" s="8" t="inlineStr">
+        <is>
+          <t>+$425.18K</t>
+        </is>
+      </c>
+      <c r="F37" s="6" t="inlineStr">
+        <is>
+          <t>+$4.44M</t>
+        </is>
+      </c>
+      <c r="G37" s="6" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H37" s="6" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
@@ -5322,28 +5240,28 @@
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>NQ</t>
+          <t>GC</t>
         </is>
       </c>
       <c r="B38" s="5" t="n">
-        <v>29596.15</v>
+        <v>4076.07</v>
       </c>
       <c r="C38" s="5" t="n">
-        <v>724</v>
+        <v>86</v>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>QQQ</t>
-        </is>
-      </c>
-      <c r="E38" s="9" t="inlineStr">
-        <is>
-          <t>+$425.18K</t>
+          <t>GDX</t>
+        </is>
+      </c>
+      <c r="E38" s="8" t="inlineStr">
+        <is>
+          <t>+$3.23M</t>
         </is>
       </c>
       <c r="F38" s="6" t="inlineStr">
         <is>
-          <t>+$4.44M</t>
+          <t>+$4.08M</t>
         </is>
       </c>
       <c r="G38" s="6" t="inlineStr">
@@ -5353,7 +5271,7 @@
       </c>
       <c r="H38" s="6" t="inlineStr">
         <is>
-          <t>valley</t>
+          <t>peak</t>
         </is>
       </c>
     </row>
@@ -5364,70 +5282,70 @@
         </is>
       </c>
       <c r="B39" s="5" t="n">
-        <v>4076.07</v>
+        <v>4121.59</v>
       </c>
       <c r="C39" s="5" t="n">
-        <v>86</v>
+        <v>380</v>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
+          <t>GLD</t>
+        </is>
+      </c>
+      <c r="E39" s="8" t="inlineStr">
+        <is>
+          <t>+$731.57K</t>
+        </is>
+      </c>
+      <c r="F39" s="6" t="inlineStr">
+        <is>
+          <t>+$3.89M</t>
+        </is>
+      </c>
+      <c r="G39" s="6" t="inlineStr">
+        <is>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H39" s="6" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>GC</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="n">
+        <v>4407.85</v>
+      </c>
+      <c r="C40" s="2" t="n">
+        <v>93</v>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
           <t>GDX</t>
         </is>
       </c>
-      <c r="E39" s="9" t="inlineStr">
-        <is>
-          <t>+$3.23M</t>
-        </is>
-      </c>
-      <c r="F39" s="6" t="inlineStr">
-        <is>
-          <t>+$4.08M</t>
-        </is>
-      </c>
-      <c r="G39" s="6" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H39" s="6" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="6" t="inlineStr">
-        <is>
-          <t>GC</t>
-        </is>
-      </c>
-      <c r="B40" s="5" t="n">
-        <v>4121.59</v>
-      </c>
-      <c r="C40" s="5" t="n">
-        <v>380</v>
-      </c>
-      <c r="D40" s="6" t="inlineStr">
-        <is>
-          <t>GLD</t>
-        </is>
-      </c>
       <c r="E40" s="9" t="inlineStr">
         <is>
-          <t>+$731.57K</t>
-        </is>
-      </c>
-      <c r="F40" s="6" t="inlineStr">
-        <is>
-          <t>+$3.89M</t>
-        </is>
-      </c>
-      <c r="G40" s="6" t="inlineStr">
-        <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H40" s="6" t="inlineStr"/>
+          <t>+$3.25M</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>+$3.38M</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
@@ -5436,24 +5354,24 @@
         </is>
       </c>
       <c r="B41" s="2" t="n">
-        <v>4407.85</v>
+        <v>4360.45</v>
       </c>
       <c r="C41" s="2" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
           <t>GDX</t>
         </is>
       </c>
-      <c r="E41" s="8" t="inlineStr">
-        <is>
-          <t>+$3.25M</t>
+      <c r="E41" s="9" t="inlineStr">
+        <is>
+          <t>+$3.08M</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>+$3.38M</t>
+          <t>+$3.20M</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
@@ -5468,114 +5386,110 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="3" t="inlineStr">
-        <is>
-          <t>GC</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="n">
-        <v>4360.45</v>
-      </c>
-      <c r="C42" s="2" t="n">
-        <v>92</v>
-      </c>
-      <c r="D42" s="3" t="inlineStr">
-        <is>
-          <t>GDX</t>
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t>CL</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>98.41</v>
+      </c>
+      <c r="C42" s="5" t="n">
+        <v>160</v>
+      </c>
+      <c r="D42" s="6" t="inlineStr">
+        <is>
+          <t>USO</t>
         </is>
       </c>
       <c r="E42" s="8" t="inlineStr">
         <is>
+          <t>+$1.54M</t>
+        </is>
+      </c>
+      <c r="F42" s="6" t="inlineStr">
+        <is>
           <t>+$3.08M</t>
         </is>
       </c>
-      <c r="F42" s="3" t="inlineStr">
-        <is>
-          <t>+$3.20M</t>
-        </is>
-      </c>
-      <c r="G42" s="3" t="inlineStr">
+      <c r="G42" s="6" t="inlineStr">
+        <is>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H42" s="6" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>CL</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="n">
+        <v>99.64</v>
+      </c>
+      <c r="C43" s="2" t="n">
+        <v>162</v>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>USO</t>
+        </is>
+      </c>
+      <c r="E43" s="9" t="inlineStr">
+        <is>
+          <t>+$2.93M</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>+$3.02M</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="H42" s="3" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="6" t="inlineStr">
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="inlineStr">
         <is>
           <t>CL</t>
         </is>
       </c>
-      <c r="B43" s="5" t="n">
-        <v>98.41</v>
-      </c>
-      <c r="C43" s="5" t="n">
-        <v>160</v>
-      </c>
-      <c r="D43" s="6" t="inlineStr">
+      <c r="B44" s="5" t="n">
+        <v>97.18000000000001</v>
+      </c>
+      <c r="C44" s="5" t="n">
+        <v>158</v>
+      </c>
+      <c r="D44" s="6" t="inlineStr">
         <is>
           <t>USO</t>
         </is>
       </c>
-      <c r="E43" s="9" t="inlineStr">
-        <is>
-          <t>+$1.54M</t>
-        </is>
-      </c>
-      <c r="F43" s="6" t="inlineStr">
-        <is>
-          <t>+$3.08M</t>
-        </is>
-      </c>
-      <c r="G43" s="6" t="inlineStr">
+      <c r="E44" s="8" t="inlineStr">
+        <is>
+          <t>+$1.68M</t>
+        </is>
+      </c>
+      <c r="F44" s="6" t="inlineStr">
+        <is>
+          <t>+$2.72M</t>
+        </is>
+      </c>
+      <c r="G44" s="6" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="H43" s="6" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="3" t="inlineStr">
-        <is>
-          <t>CL</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="n">
-        <v>99.64</v>
-      </c>
-      <c r="C44" s="2" t="n">
-        <v>162</v>
-      </c>
-      <c r="D44" s="3" t="inlineStr">
-        <is>
-          <t>USO</t>
-        </is>
-      </c>
-      <c r="E44" s="8" t="inlineStr">
-        <is>
-          <t>+$2.93M</t>
-        </is>
-      </c>
-      <c r="F44" s="3" t="inlineStr">
-        <is>
-          <t>+$3.02M</t>
-        </is>
-      </c>
-      <c r="G44" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H44" s="3" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
+      <c r="H44" s="6" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
@@ -5584,58 +5498,62 @@
         </is>
       </c>
       <c r="B45" s="5" t="n">
-        <v>97.18000000000001</v>
+        <v>97.8</v>
       </c>
       <c r="C45" s="5" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
           <t>USO</t>
         </is>
       </c>
-      <c r="E45" s="9" t="inlineStr">
-        <is>
-          <t>+$1.68M</t>
+      <c r="E45" s="8" t="inlineStr">
+        <is>
+          <t>+$1.74M</t>
         </is>
       </c>
       <c r="F45" s="6" t="inlineStr">
         <is>
-          <t>+$2.72M</t>
+          <t>+$2.29M</t>
         </is>
       </c>
       <c r="G45" s="6" t="inlineStr">
         <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H45" s="6" t="inlineStr"/>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H45" s="6" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="6" t="inlineStr">
         <is>
-          <t>CL</t>
+          <t>NQ</t>
         </is>
       </c>
       <c r="B46" s="5" t="n">
-        <v>97.8</v>
+        <v>29884.01</v>
       </c>
       <c r="C46" s="5" t="n">
-        <v>159</v>
+        <v>731</v>
       </c>
       <c r="D46" s="6" t="inlineStr">
         <is>
-          <t>USO</t>
-        </is>
-      </c>
-      <c r="E46" s="9" t="inlineStr">
-        <is>
-          <t>+$1.74M</t>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="E46" s="8" t="inlineStr">
+        <is>
+          <t>+$1.58M</t>
         </is>
       </c>
       <c r="F46" s="6" t="inlineStr">
         <is>
-          <t>+$2.29M</t>
+          <t>+$2.22M</t>
         </is>
       </c>
       <c r="G46" s="6" t="inlineStr">
@@ -5645,7 +5563,7 @@
       </c>
       <c r="H46" s="6" t="inlineStr">
         <is>
-          <t>peak</t>
+          <t>valley</t>
         </is>
       </c>
     </row>
@@ -5656,24 +5574,24 @@
         </is>
       </c>
       <c r="B47" s="5" t="n">
-        <v>29884.01</v>
+        <v>29801.77</v>
       </c>
       <c r="C47" s="5" t="n">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
           <t>QQQ</t>
         </is>
       </c>
-      <c r="E47" s="9" t="inlineStr">
-        <is>
-          <t>+$1.58M</t>
+      <c r="E47" s="8" t="inlineStr">
+        <is>
+          <t>+$631.92K</t>
         </is>
       </c>
       <c r="F47" s="6" t="inlineStr">
         <is>
-          <t>+$2.22M</t>
+          <t>+$1.94M</t>
         </is>
       </c>
       <c r="G47" s="6" t="inlineStr">
@@ -5694,24 +5612,24 @@
         </is>
       </c>
       <c r="B48" s="5" t="n">
-        <v>29801.77</v>
+        <v>30048.51</v>
       </c>
       <c r="C48" s="5" t="n">
-        <v>729</v>
+        <v>735</v>
       </c>
       <c r="D48" s="6" t="inlineStr">
         <is>
           <t>QQQ</t>
         </is>
       </c>
-      <c r="E48" s="9" t="inlineStr">
-        <is>
-          <t>+$631.92K</t>
+      <c r="E48" s="8" t="inlineStr">
+        <is>
+          <t>+$462.77K</t>
         </is>
       </c>
       <c r="F48" s="6" t="inlineStr">
         <is>
-          <t>+$1.94M</t>
+          <t>+$1.93M</t>
         </is>
       </c>
       <c r="G48" s="6" t="inlineStr">
@@ -5726,68 +5644,68 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="6" t="inlineStr">
-        <is>
-          <t>NQ</t>
-        </is>
-      </c>
-      <c r="B49" s="5" t="n">
-        <v>30048.51</v>
-      </c>
-      <c r="C49" s="5" t="n">
-        <v>735</v>
-      </c>
-      <c r="D49" s="6" t="inlineStr">
-        <is>
-          <t>QQQ</t>
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>CL</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="n">
+        <v>96.56999999999999</v>
+      </c>
+      <c r="C49" s="2" t="n">
+        <v>157</v>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>USO</t>
         </is>
       </c>
       <c r="E49" s="9" t="inlineStr">
         <is>
-          <t>+$462.77K</t>
-        </is>
-      </c>
-      <c r="F49" s="6" t="inlineStr">
-        <is>
-          <t>+$1.93M</t>
-        </is>
-      </c>
-      <c r="G49" s="6" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H49" s="6" t="inlineStr">
-        <is>
-          <t>valley</t>
+          <t>+$821.39K</t>
+        </is>
+      </c>
+      <c r="F49" s="3" t="inlineStr">
+        <is>
+          <t>+$1.70M</t>
+        </is>
+      </c>
+      <c r="G49" s="3" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H49" s="3" t="inlineStr">
+        <is>
+          <t>peak</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>GC</t>
         </is>
       </c>
       <c r="B50" s="5" t="n">
-        <v>7791.83</v>
+        <v>4110.74</v>
       </c>
       <c r="C50" s="5" t="n">
-        <v>7795</v>
+        <v>379</v>
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
-          <t>SPX</t>
-        </is>
-      </c>
-      <c r="E50" s="9" t="inlineStr">
-        <is>
-          <t>+$1.67M</t>
+          <t>GLD</t>
+        </is>
+      </c>
+      <c r="E50" s="7" t="inlineStr">
+        <is>
+          <t>-$723.70K</t>
         </is>
       </c>
       <c r="F50" s="6" t="inlineStr">
         <is>
-          <t>+$1.85M</t>
+          <t>+$1.41M</t>
         </is>
       </c>
       <c r="G50" s="6" t="inlineStr">
@@ -5802,42 +5720,38 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="3" t="inlineStr">
-        <is>
-          <t>CL</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="n">
-        <v>96.56999999999999</v>
-      </c>
-      <c r="C51" s="2" t="n">
-        <v>157</v>
-      </c>
-      <c r="D51" s="3" t="inlineStr">
-        <is>
-          <t>USO</t>
-        </is>
-      </c>
-      <c r="E51" s="8" t="inlineStr">
-        <is>
-          <t>+$821.39K</t>
-        </is>
-      </c>
-      <c r="F51" s="3" t="inlineStr">
-        <is>
-          <t>+$1.70M</t>
-        </is>
-      </c>
-      <c r="G51" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H51" s="3" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t>GC</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>3933.89</v>
+      </c>
+      <c r="C51" s="5" t="n">
+        <v>83</v>
+      </c>
+      <c r="D51" s="6" t="inlineStr">
+        <is>
+          <t>GDX</t>
+        </is>
+      </c>
+      <c r="E51" s="7" t="inlineStr">
+        <is>
+          <t>-$1.06M</t>
+        </is>
+      </c>
+      <c r="F51" s="6" t="inlineStr">
+        <is>
+          <t>+$1.32M</t>
+        </is>
+      </c>
+      <c r="G51" s="6" t="inlineStr">
+        <is>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H51" s="6" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="6" t="inlineStr">
@@ -5846,24 +5760,24 @@
         </is>
       </c>
       <c r="B52" s="5" t="n">
-        <v>4110.74</v>
+        <v>4143.28</v>
       </c>
       <c r="C52" s="5" t="n">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="D52" s="6" t="inlineStr">
         <is>
           <t>GLD</t>
         </is>
       </c>
-      <c r="E52" s="7" t="inlineStr">
-        <is>
-          <t>-$723.70K</t>
+      <c r="E52" s="8" t="inlineStr">
+        <is>
+          <t>+$969.66K</t>
         </is>
       </c>
       <c r="F52" s="6" t="inlineStr">
         <is>
-          <t>+$1.41M</t>
+          <t>+$1.10M</t>
         </is>
       </c>
       <c r="G52" s="6" t="inlineStr">
@@ -5873,153 +5787,157 @@
       </c>
       <c r="H52" s="6" t="inlineStr">
         <is>
-          <t>valley</t>
+          <t>peak</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="6" t="inlineStr">
-        <is>
-          <t>GC</t>
-        </is>
-      </c>
-      <c r="B53" s="5" t="n">
-        <v>3933.89</v>
-      </c>
-      <c r="C53" s="5" t="n">
-        <v>83</v>
-      </c>
-      <c r="D53" s="6" t="inlineStr">
-        <is>
-          <t>GDX</t>
-        </is>
-      </c>
-      <c r="E53" s="7" t="inlineStr">
-        <is>
-          <t>-$1.06M</t>
-        </is>
-      </c>
-      <c r="F53" s="6" t="inlineStr">
-        <is>
-          <t>+$1.32M</t>
-        </is>
-      </c>
-      <c r="G53" s="6" t="inlineStr">
-        <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H53" s="6" t="inlineStr"/>
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>CL</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="n">
+        <v>104.56</v>
+      </c>
+      <c r="C53" s="2" t="n">
+        <v>170</v>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>USO</t>
+        </is>
+      </c>
+      <c r="E53" s="9" t="inlineStr">
+        <is>
+          <t>+$1.03M</t>
+        </is>
+      </c>
+      <c r="F53" s="3" t="inlineStr">
+        <is>
+          <t>+$1.07M</t>
+        </is>
+      </c>
+      <c r="G53" s="3" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H53" s="3" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="6" t="inlineStr">
         <is>
+          <t>CL</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>95.34</v>
+      </c>
+      <c r="C54" s="5" t="n">
+        <v>155</v>
+      </c>
+      <c r="D54" s="6" t="inlineStr">
+        <is>
+          <t>USO</t>
+        </is>
+      </c>
+      <c r="E54" s="7" t="inlineStr">
+        <is>
+          <t>-$299.36K</t>
+        </is>
+      </c>
+      <c r="F54" s="6" t="inlineStr">
+        <is>
+          <t>+$985.83K</t>
+        </is>
+      </c>
+      <c r="G54" s="6" t="inlineStr">
+        <is>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H54" s="6" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="6" t="inlineStr">
+        <is>
           <t>GC</t>
         </is>
       </c>
-      <c r="B54" s="5" t="n">
-        <v>4143.28</v>
-      </c>
-      <c r="C54" s="5" t="n">
-        <v>382</v>
-      </c>
-      <c r="D54" s="6" t="inlineStr">
+      <c r="B55" s="5" t="n">
+        <v>4067.36</v>
+      </c>
+      <c r="C55" s="5" t="n">
+        <v>375</v>
+      </c>
+      <c r="D55" s="6" t="inlineStr">
         <is>
           <t>GLD</t>
         </is>
       </c>
-      <c r="E54" s="9" t="inlineStr">
-        <is>
-          <t>+$969.66K</t>
-        </is>
-      </c>
-      <c r="F54" s="6" t="inlineStr">
-        <is>
-          <t>+$1.10M</t>
-        </is>
-      </c>
-      <c r="G54" s="6" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H54" s="6" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="3" t="inlineStr">
-        <is>
-          <t>CL</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="n">
-        <v>104.56</v>
-      </c>
-      <c r="C55" s="2" t="n">
-        <v>170</v>
-      </c>
-      <c r="D55" s="3" t="inlineStr">
-        <is>
-          <t>USO</t>
-        </is>
-      </c>
-      <c r="E55" s="8" t="inlineStr">
-        <is>
-          <t>+$1.03M</t>
-        </is>
-      </c>
-      <c r="F55" s="3" t="inlineStr">
-        <is>
-          <t>+$1.07M</t>
-        </is>
-      </c>
-      <c r="G55" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H55" s="3" t="inlineStr">
-        <is>
-          <t>peak</t>
+      <c r="E55" s="7" t="inlineStr">
+        <is>
+          <t>-$860.50K</t>
+        </is>
+      </c>
+      <c r="F55" s="6" t="inlineStr">
+        <is>
+          <t>+$959.88K</t>
+        </is>
+      </c>
+      <c r="G55" s="6" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H55" s="6" t="inlineStr">
+        <is>
+          <t>valley</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="6" t="inlineStr">
         <is>
-          <t>CL</t>
+          <t>GC</t>
         </is>
       </c>
       <c r="B56" s="5" t="n">
-        <v>95.34</v>
+        <v>4164.97</v>
       </c>
       <c r="C56" s="5" t="n">
-        <v>155</v>
+        <v>384</v>
       </c>
       <c r="D56" s="6" t="inlineStr">
         <is>
-          <t>USO</t>
-        </is>
-      </c>
-      <c r="E56" s="7" t="inlineStr">
-        <is>
-          <t>-$299.36K</t>
+          <t>GLD</t>
+        </is>
+      </c>
+      <c r="E56" s="8" t="inlineStr">
+        <is>
+          <t>+$796.41K</t>
         </is>
       </c>
       <c r="F56" s="6" t="inlineStr">
         <is>
-          <t>+$985.83K</t>
+          <t>+$807.24K</t>
         </is>
       </c>
       <c r="G56" s="6" t="inlineStr">
         <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H56" s="6" t="inlineStr"/>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H56" s="6" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="6" t="inlineStr">
@@ -6028,24 +5946,24 @@
         </is>
       </c>
       <c r="B57" s="5" t="n">
-        <v>4067.36</v>
+        <v>4099.9</v>
       </c>
       <c r="C57" s="5" t="n">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="D57" s="6" t="inlineStr">
         <is>
           <t>GLD</t>
         </is>
       </c>
-      <c r="E57" s="7" t="inlineStr">
-        <is>
-          <t>-$860.50K</t>
+      <c r="E57" s="8" t="inlineStr">
+        <is>
+          <t>+$186.16K</t>
         </is>
       </c>
       <c r="F57" s="6" t="inlineStr">
         <is>
-          <t>+$959.88K</t>
+          <t>+$777.14K</t>
         </is>
       </c>
       <c r="G57" s="6" t="inlineStr">
@@ -6055,35 +5973,35 @@
       </c>
       <c r="H57" s="6" t="inlineStr">
         <is>
-          <t>valley</t>
+          <t>peak</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="6" t="inlineStr">
         <is>
-          <t>GC</t>
+          <t>CL</t>
         </is>
       </c>
       <c r="B58" s="5" t="n">
-        <v>4164.97</v>
+        <v>99.03</v>
       </c>
       <c r="C58" s="5" t="n">
-        <v>384</v>
+        <v>161</v>
       </c>
       <c r="D58" s="6" t="inlineStr">
         <is>
-          <t>GLD</t>
-        </is>
-      </c>
-      <c r="E58" s="9" t="inlineStr">
-        <is>
-          <t>+$796.41K</t>
+          <t>USO</t>
+        </is>
+      </c>
+      <c r="E58" s="8" t="inlineStr">
+        <is>
+          <t>+$230.88K</t>
         </is>
       </c>
       <c r="F58" s="6" t="inlineStr">
         <is>
-          <t>+$807.24K</t>
+          <t>+$675.61K</t>
         </is>
       </c>
       <c r="G58" s="6" t="inlineStr">
@@ -6093,7 +6011,7 @@
       </c>
       <c r="H58" s="6" t="inlineStr">
         <is>
-          <t>peak</t>
+          <t>valley</t>
         </is>
       </c>
     </row>
@@ -6104,24 +6022,24 @@
         </is>
       </c>
       <c r="B59" s="5" t="n">
-        <v>4099.9</v>
+        <v>4194.57</v>
       </c>
       <c r="C59" s="5" t="n">
-        <v>378</v>
+        <v>88.5</v>
       </c>
       <c r="D59" s="6" t="inlineStr">
         <is>
-          <t>GLD</t>
-        </is>
-      </c>
-      <c r="E59" s="9" t="inlineStr">
-        <is>
-          <t>+$186.16K</t>
+          <t>GDX</t>
+        </is>
+      </c>
+      <c r="E59" s="8" t="inlineStr">
+        <is>
+          <t>+$14.47K</t>
         </is>
       </c>
       <c r="F59" s="6" t="inlineStr">
         <is>
-          <t>+$777.14K</t>
+          <t>+$606.28K</t>
         </is>
       </c>
       <c r="G59" s="6" t="inlineStr">
@@ -6131,35 +6049,35 @@
       </c>
       <c r="H59" s="6" t="inlineStr">
         <is>
-          <t>peak</t>
+          <t>valley</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="6" t="inlineStr">
         <is>
-          <t>CL</t>
+          <t>RTY</t>
         </is>
       </c>
       <c r="B60" s="5" t="n">
-        <v>99.03</v>
+        <v>2826.86</v>
       </c>
       <c r="C60" s="5" t="n">
-        <v>161</v>
+        <v>281</v>
       </c>
       <c r="D60" s="6" t="inlineStr">
         <is>
-          <t>USO</t>
-        </is>
-      </c>
-      <c r="E60" s="9" t="inlineStr">
-        <is>
-          <t>+$230.88K</t>
+          <t>IWM</t>
+        </is>
+      </c>
+      <c r="E60" s="8" t="inlineStr">
+        <is>
+          <t>+$580.02K</t>
         </is>
       </c>
       <c r="F60" s="6" t="inlineStr">
         <is>
-          <t>+$675.61K</t>
+          <t>+$602.62K</t>
         </is>
       </c>
       <c r="G60" s="6" t="inlineStr">
@@ -6176,66 +6094,62 @@
     <row r="61">
       <c r="A61" s="6" t="inlineStr">
         <is>
-          <t>GC</t>
+          <t>CL</t>
         </is>
       </c>
       <c r="B61" s="5" t="n">
-        <v>4194.57</v>
+        <v>92.26000000000001</v>
       </c>
       <c r="C61" s="5" t="n">
-        <v>88.5</v>
+        <v>150</v>
       </c>
       <c r="D61" s="6" t="inlineStr">
         <is>
-          <t>GDX</t>
-        </is>
-      </c>
-      <c r="E61" s="9" t="inlineStr">
-        <is>
-          <t>+$14.47K</t>
+          <t>USO</t>
+        </is>
+      </c>
+      <c r="E61" s="7" t="inlineStr">
+        <is>
+          <t>-$284.17K</t>
         </is>
       </c>
       <c r="F61" s="6" t="inlineStr">
         <is>
-          <t>+$606.28K</t>
+          <t>+$600.78K</t>
         </is>
       </c>
       <c r="G61" s="6" t="inlineStr">
         <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H61" s="6" t="inlineStr">
-        <is>
-          <t>valley</t>
-        </is>
-      </c>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H61" s="6" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="6" t="inlineStr">
         <is>
-          <t>RTY</t>
+          <t>GC</t>
         </is>
       </c>
       <c r="B62" s="5" t="n">
-        <v>2826.86</v>
+        <v>4154.13</v>
       </c>
       <c r="C62" s="5" t="n">
-        <v>281</v>
+        <v>383</v>
       </c>
       <c r="D62" s="6" t="inlineStr">
         <is>
-          <t>IWM</t>
-        </is>
-      </c>
-      <c r="E62" s="9" t="inlineStr">
-        <is>
-          <t>+$580.02K</t>
+          <t>GLD</t>
+        </is>
+      </c>
+      <c r="E62" s="8" t="inlineStr">
+        <is>
+          <t>+$484.07K</t>
         </is>
       </c>
       <c r="F62" s="6" t="inlineStr">
         <is>
-          <t>+$602.62K</t>
+          <t>+$541.37K</t>
         </is>
       </c>
       <c r="G62" s="6" t="inlineStr">
@@ -6256,24 +6170,24 @@
         </is>
       </c>
       <c r="B63" s="5" t="n">
-        <v>92.26000000000001</v>
+        <v>103.33</v>
       </c>
       <c r="C63" s="5" t="n">
-        <v>150</v>
+        <v>168</v>
       </c>
       <c r="D63" s="6" t="inlineStr">
         <is>
           <t>USO</t>
         </is>
       </c>
-      <c r="E63" s="7" t="inlineStr">
-        <is>
-          <t>-$284.17K</t>
+      <c r="E63" s="8" t="inlineStr">
+        <is>
+          <t>+$478.68K</t>
         </is>
       </c>
       <c r="F63" s="6" t="inlineStr">
         <is>
-          <t>+$600.78K</t>
+          <t>+$502.23K</t>
         </is>
       </c>
       <c r="G63" s="6" t="inlineStr">
@@ -6290,24 +6204,24 @@
         </is>
       </c>
       <c r="B64" s="5" t="n">
-        <v>4154.13</v>
+        <v>4099.77</v>
       </c>
       <c r="C64" s="5" t="n">
-        <v>383</v>
+        <v>86.5</v>
       </c>
       <c r="D64" s="6" t="inlineStr">
         <is>
-          <t>GLD</t>
-        </is>
-      </c>
-      <c r="E64" s="9" t="inlineStr">
-        <is>
-          <t>+$484.07K</t>
+          <t>GDX</t>
+        </is>
+      </c>
+      <c r="E64" s="7" t="inlineStr">
+        <is>
+          <t>-$71.92K</t>
         </is>
       </c>
       <c r="F64" s="6" t="inlineStr">
         <is>
-          <t>+$541.37K</t>
+          <t>+$496.81K</t>
         </is>
       </c>
       <c r="G64" s="6" t="inlineStr">
@@ -6328,104 +6242,104 @@
         </is>
       </c>
       <c r="B65" s="5" t="n">
-        <v>103.33</v>
+        <v>96.88</v>
       </c>
       <c r="C65" s="5" t="n">
-        <v>168</v>
+        <v>157.5</v>
       </c>
       <c r="D65" s="6" t="inlineStr">
         <is>
           <t>USO</t>
         </is>
       </c>
-      <c r="E65" s="9" t="inlineStr">
-        <is>
-          <t>+$478.68K</t>
+      <c r="E65" s="8" t="inlineStr">
+        <is>
+          <t>+$127.52K</t>
         </is>
       </c>
       <c r="F65" s="6" t="inlineStr">
         <is>
-          <t>+$502.23K</t>
+          <t>+$449.41K</t>
         </is>
       </c>
       <c r="G65" s="6" t="inlineStr">
         <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H65" s="6" t="inlineStr"/>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H65" s="6" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="6" t="inlineStr">
         <is>
-          <t>GC</t>
+          <t>CL</t>
         </is>
       </c>
       <c r="B66" s="5" t="n">
-        <v>4099.77</v>
+        <v>89.19</v>
       </c>
       <c r="C66" s="5" t="n">
-        <v>86.5</v>
+        <v>145</v>
       </c>
       <c r="D66" s="6" t="inlineStr">
         <is>
-          <t>GDX</t>
+          <t>USO</t>
         </is>
       </c>
       <c r="E66" s="7" t="inlineStr">
         <is>
-          <t>-$71.92K</t>
+          <t>-$291.76K</t>
         </is>
       </c>
       <c r="F66" s="6" t="inlineStr">
         <is>
-          <t>+$496.81K</t>
+          <t>+$375.16K</t>
         </is>
       </c>
       <c r="G66" s="6" t="inlineStr">
         <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H66" s="6" t="inlineStr">
-        <is>
-          <t>valley</t>
-        </is>
-      </c>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H66" s="6" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" s="6" t="inlineStr">
-        <is>
-          <t>CL</t>
-        </is>
-      </c>
-      <c r="B67" s="5" t="n">
-        <v>96.88</v>
-      </c>
-      <c r="C67" s="5" t="n">
-        <v>157.5</v>
-      </c>
-      <c r="D67" s="6" t="inlineStr">
-        <is>
-          <t>USO</t>
-        </is>
-      </c>
-      <c r="E67" s="9" t="inlineStr">
-        <is>
-          <t>+$127.52K</t>
-        </is>
-      </c>
-      <c r="F67" s="6" t="inlineStr">
-        <is>
-          <t>+$449.41K</t>
-        </is>
-      </c>
-      <c r="G67" s="6" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H67" s="6" t="inlineStr">
+      <c r="A67" s="3" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="n">
+        <v>29622.98</v>
+      </c>
+      <c r="C67" s="2" t="n">
+        <v>29800</v>
+      </c>
+      <c r="D67" s="3" t="inlineStr">
+        <is>
+          <t>NDX</t>
+        </is>
+      </c>
+      <c r="E67" s="4" t="inlineStr">
+        <is>
+          <t>-$88.57K</t>
+        </is>
+      </c>
+      <c r="F67" s="3" t="inlineStr">
+        <is>
+          <t>+$291.96K</t>
+        </is>
+      </c>
+      <c r="G67" s="3" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H67" s="3" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
@@ -6434,36 +6348,40 @@
     <row r="68">
       <c r="A68" s="6" t="inlineStr">
         <is>
-          <t>CL</t>
+          <t>GC</t>
         </is>
       </c>
       <c r="B68" s="5" t="n">
-        <v>89.19</v>
+        <v>4336.75</v>
       </c>
       <c r="C68" s="5" t="n">
-        <v>145</v>
+        <v>91.5</v>
       </c>
       <c r="D68" s="6" t="inlineStr">
         <is>
-          <t>USO</t>
-        </is>
-      </c>
-      <c r="E68" s="7" t="inlineStr">
-        <is>
-          <t>-$291.76K</t>
+          <t>GDX</t>
+        </is>
+      </c>
+      <c r="E68" s="8" t="inlineStr">
+        <is>
+          <t>+$193.31K</t>
         </is>
       </c>
       <c r="F68" s="6" t="inlineStr">
         <is>
-          <t>+$375.16K</t>
+          <t>+$249.72K</t>
         </is>
       </c>
       <c r="G68" s="6" t="inlineStr">
         <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H68" s="6" t="inlineStr"/>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H68" s="6" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
@@ -6472,10 +6390,10 @@
         </is>
       </c>
       <c r="B69" s="2" t="n">
-        <v>29622.98</v>
+        <v>29522.98</v>
       </c>
       <c r="C69" s="2" t="n">
-        <v>29800</v>
+        <v>29700</v>
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
@@ -6484,12 +6402,12 @@
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>-$88.57K</t>
+          <t>-$116.31K</t>
         </is>
       </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
-          <t>+$291.96K</t>
+          <t>+$217.70K</t>
         </is>
       </c>
       <c r="G69" s="3" t="inlineStr">
@@ -6506,40 +6424,36 @@
     <row r="70">
       <c r="A70" s="6" t="inlineStr">
         <is>
-          <t>GC</t>
+          <t>NQ</t>
         </is>
       </c>
       <c r="B70" s="5" t="n">
-        <v>4336.75</v>
+        <v>29652.98</v>
       </c>
       <c r="C70" s="5" t="n">
-        <v>91.5</v>
+        <v>29830</v>
       </c>
       <c r="D70" s="6" t="inlineStr">
         <is>
-          <t>GDX</t>
-        </is>
-      </c>
-      <c r="E70" s="9" t="inlineStr">
-        <is>
-          <t>+$193.31K</t>
+          <t>NDX</t>
+        </is>
+      </c>
+      <c r="E70" s="8" t="inlineStr">
+        <is>
+          <t>+$127.94K</t>
         </is>
       </c>
       <c r="F70" s="6" t="inlineStr">
         <is>
-          <t>+$249.72K</t>
+          <t>+$186.99K</t>
         </is>
       </c>
       <c r="G70" s="6" t="inlineStr">
         <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H70" s="6" t="inlineStr">
-        <is>
-          <t>valley</t>
-        </is>
-      </c>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H70" s="6" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
@@ -6548,24 +6462,24 @@
         </is>
       </c>
       <c r="B71" s="2" t="n">
-        <v>29522.98</v>
+        <v>29722.98</v>
       </c>
       <c r="C71" s="2" t="n">
-        <v>29700</v>
+        <v>29900</v>
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="E71" s="4" t="inlineStr">
-        <is>
-          <t>-$116.31K</t>
+      <c r="E71" s="9" t="inlineStr">
+        <is>
+          <t>+$82.01K</t>
         </is>
       </c>
       <c r="F71" s="3" t="inlineStr">
         <is>
-          <t>+$217.70K</t>
+          <t>+$180.43K</t>
         </is>
       </c>
       <c r="G71" s="3" t="inlineStr">
@@ -6575,43 +6489,47 @@
       </c>
       <c r="H71" s="3" t="inlineStr">
         <is>
-          <t>valley</t>
+          <t>peak</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="6" t="inlineStr">
+      <c r="A72" s="3" t="inlineStr">
         <is>
           <t>NQ</t>
         </is>
       </c>
-      <c r="B72" s="5" t="n">
-        <v>29652.98</v>
-      </c>
-      <c r="C72" s="5" t="n">
-        <v>29830</v>
-      </c>
-      <c r="D72" s="6" t="inlineStr">
+      <c r="B72" s="2" t="n">
+        <v>29802.98</v>
+      </c>
+      <c r="C72" s="2" t="n">
+        <v>29980</v>
+      </c>
+      <c r="D72" s="3" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
       <c r="E72" s="9" t="inlineStr">
         <is>
-          <t>+$127.94K</t>
-        </is>
-      </c>
-      <c r="F72" s="6" t="inlineStr">
-        <is>
-          <t>+$186.99K</t>
-        </is>
-      </c>
-      <c r="G72" s="6" t="inlineStr">
-        <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H72" s="6" t="inlineStr"/>
+          <t>+$164.02K</t>
+        </is>
+      </c>
+      <c r="F72" s="3" t="inlineStr">
+        <is>
+          <t>+$169.99K</t>
+        </is>
+      </c>
+      <c r="G72" s="3" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H72" s="3" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
@@ -6620,24 +6538,24 @@
         </is>
       </c>
       <c r="B73" s="2" t="n">
-        <v>29722.98</v>
+        <v>29772.98</v>
       </c>
       <c r="C73" s="2" t="n">
-        <v>29900</v>
+        <v>29950</v>
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="E73" s="8" t="inlineStr">
-        <is>
-          <t>+$82.01K</t>
+      <c r="E73" s="9" t="inlineStr">
+        <is>
+          <t>+$98.41K</t>
         </is>
       </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
-          <t>+$180.43K</t>
+          <t>+$169.99K</t>
         </is>
       </c>
       <c r="G73" s="3" t="inlineStr">
@@ -6658,24 +6576,24 @@
         </is>
       </c>
       <c r="B74" s="2" t="n">
-        <v>29802.98</v>
+        <v>29822.98</v>
       </c>
       <c r="C74" s="2" t="n">
-        <v>29980</v>
+        <v>30000</v>
       </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="E74" s="8" t="inlineStr">
-        <is>
-          <t>+$164.02K</t>
+      <c r="E74" s="9" t="inlineStr">
+        <is>
+          <t>+$83.50K</t>
         </is>
       </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
-          <t>+$169.99K</t>
+          <t>+$161.04K</t>
         </is>
       </c>
       <c r="G74" s="3" t="inlineStr">
@@ -6696,24 +6614,24 @@
         </is>
       </c>
       <c r="B75" s="2" t="n">
-        <v>29772.98</v>
+        <v>29682.98</v>
       </c>
       <c r="C75" s="2" t="n">
-        <v>29950</v>
+        <v>29860</v>
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="E75" s="8" t="inlineStr">
-        <is>
-          <t>+$98.41K</t>
+      <c r="E75" s="4" t="inlineStr">
+        <is>
+          <t>-$75.45K</t>
         </is>
       </c>
       <c r="F75" s="3" t="inlineStr">
         <is>
-          <t>+$169.99K</t>
+          <t>+$160.74K</t>
         </is>
       </c>
       <c r="G75" s="3" t="inlineStr">
@@ -6723,85 +6641,81 @@
       </c>
       <c r="H75" s="3" t="inlineStr">
         <is>
-          <t>peak</t>
+          <t>valley</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="3" t="inlineStr">
+      <c r="A76" s="6" t="inlineStr">
         <is>
           <t>NQ</t>
         </is>
       </c>
-      <c r="B76" s="2" t="n">
-        <v>29822.98</v>
-      </c>
-      <c r="C76" s="2" t="n">
-        <v>30000</v>
-      </c>
-      <c r="D76" s="3" t="inlineStr">
+      <c r="B76" s="5" t="n">
+        <v>29712.98</v>
+      </c>
+      <c r="C76" s="5" t="n">
+        <v>29890</v>
+      </c>
+      <c r="D76" s="6" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="E76" s="8" t="inlineStr">
-        <is>
-          <t>+$83.50K</t>
-        </is>
-      </c>
-      <c r="F76" s="3" t="inlineStr">
-        <is>
-          <t>+$161.04K</t>
-        </is>
-      </c>
-      <c r="G76" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H76" s="3" t="inlineStr">
-        <is>
-          <t>peak</t>
+      <c r="E76" s="7" t="inlineStr">
+        <is>
+          <t>-$72.17K</t>
+        </is>
+      </c>
+      <c r="F76" s="6" t="inlineStr">
+        <is>
+          <t>+$157.46K</t>
+        </is>
+      </c>
+      <c r="G76" s="6" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H76" s="6" t="inlineStr">
+        <is>
+          <t>valley</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="3" t="inlineStr">
+      <c r="A77" s="6" t="inlineStr">
         <is>
           <t>NQ</t>
         </is>
       </c>
-      <c r="B77" s="2" t="n">
-        <v>29682.98</v>
-      </c>
-      <c r="C77" s="2" t="n">
-        <v>29860</v>
-      </c>
-      <c r="D77" s="3" t="inlineStr">
+      <c r="B77" s="5" t="n">
+        <v>29572.98</v>
+      </c>
+      <c r="C77" s="5" t="n">
+        <v>29750</v>
+      </c>
+      <c r="D77" s="6" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="E77" s="4" t="inlineStr">
-        <is>
-          <t>-$75.45K</t>
-        </is>
-      </c>
-      <c r="F77" s="3" t="inlineStr">
-        <is>
-          <t>+$160.74K</t>
-        </is>
-      </c>
-      <c r="G77" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H77" s="3" t="inlineStr">
-        <is>
-          <t>valley</t>
-        </is>
-      </c>
+      <c r="E77" s="7" t="inlineStr">
+        <is>
+          <t>-$65.61K</t>
+        </is>
+      </c>
+      <c r="F77" s="6" t="inlineStr">
+        <is>
+          <t>+$143.15K</t>
+        </is>
+      </c>
+      <c r="G77" s="6" t="inlineStr">
+        <is>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H77" s="6" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="6" t="inlineStr">
@@ -6810,24 +6724,24 @@
         </is>
       </c>
       <c r="B78" s="5" t="n">
-        <v>29712.98</v>
+        <v>29662.98</v>
       </c>
       <c r="C78" s="5" t="n">
-        <v>29890</v>
+        <v>29840</v>
       </c>
       <c r="D78" s="6" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="E78" s="7" t="inlineStr">
-        <is>
-          <t>-$72.17K</t>
+      <c r="E78" s="8" t="inlineStr">
+        <is>
+          <t>+$134.50K</t>
         </is>
       </c>
       <c r="F78" s="6" t="inlineStr">
         <is>
-          <t>+$157.46K</t>
+          <t>+$141.06K</t>
         </is>
       </c>
       <c r="G78" s="6" t="inlineStr">
@@ -6837,43 +6751,47 @@
       </c>
       <c r="H78" s="6" t="inlineStr">
         <is>
-          <t>valley</t>
+          <t>peak</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="6" t="inlineStr">
         <is>
-          <t>NQ</t>
+          <t>CL</t>
         </is>
       </c>
       <c r="B79" s="5" t="n">
-        <v>29572.98</v>
+        <v>103.95</v>
       </c>
       <c r="C79" s="5" t="n">
-        <v>29750</v>
+        <v>169</v>
       </c>
       <c r="D79" s="6" t="inlineStr">
         <is>
-          <t>NDX</t>
-        </is>
-      </c>
-      <c r="E79" s="7" t="inlineStr">
-        <is>
-          <t>-$65.61K</t>
+          <t>USO</t>
+        </is>
+      </c>
+      <c r="E79" s="8" t="inlineStr">
+        <is>
+          <t>+$116.02K</t>
         </is>
       </c>
       <c r="F79" s="6" t="inlineStr">
         <is>
-          <t>+$143.15K</t>
+          <t>+$121.97K</t>
         </is>
       </c>
       <c r="G79" s="6" t="inlineStr">
         <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H79" s="6" t="inlineStr"/>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H79" s="6" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="6" t="inlineStr">
@@ -6882,62 +6800,58 @@
         </is>
       </c>
       <c r="B80" s="5" t="n">
-        <v>29662.98</v>
+        <v>29472.98</v>
       </c>
       <c r="C80" s="5" t="n">
-        <v>29840</v>
+        <v>29650</v>
       </c>
       <c r="D80" s="6" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="E80" s="9" t="inlineStr">
-        <is>
-          <t>+$134.50K</t>
+      <c r="E80" s="7" t="inlineStr">
+        <is>
+          <t>-$56.36K</t>
         </is>
       </c>
       <c r="F80" s="6" t="inlineStr">
         <is>
-          <t>+$141.06K</t>
+          <t>+$115.41K</t>
         </is>
       </c>
       <c r="G80" s="6" t="inlineStr">
         <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H80" s="6" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H80" s="6" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="6" t="inlineStr">
         <is>
-          <t>CL</t>
+          <t>NQ</t>
         </is>
       </c>
       <c r="B81" s="5" t="n">
-        <v>103.95</v>
+        <v>29552.98</v>
       </c>
       <c r="C81" s="5" t="n">
-        <v>169</v>
+        <v>29730</v>
       </c>
       <c r="D81" s="6" t="inlineStr">
         <is>
-          <t>USO</t>
-        </is>
-      </c>
-      <c r="E81" s="9" t="inlineStr">
-        <is>
-          <t>+$116.02K</t>
+          <t>NDX</t>
+        </is>
+      </c>
+      <c r="E81" s="7" t="inlineStr">
+        <is>
+          <t>-$113.33K</t>
         </is>
       </c>
       <c r="F81" s="6" t="inlineStr">
         <is>
-          <t>+$121.97K</t>
+          <t>+$113.33K</t>
         </is>
       </c>
       <c r="G81" s="6" t="inlineStr">
@@ -6958,10 +6872,10 @@
         </is>
       </c>
       <c r="B82" s="5" t="n">
-        <v>29472.98</v>
+        <v>29732.98</v>
       </c>
       <c r="C82" s="5" t="n">
-        <v>29650</v>
+        <v>29910</v>
       </c>
       <c r="D82" s="6" t="inlineStr">
         <is>
@@ -6970,130 +6884,134 @@
       </c>
       <c r="E82" s="7" t="inlineStr">
         <is>
-          <t>-$56.36K</t>
+          <t>-$6.56K</t>
         </is>
       </c>
       <c r="F82" s="6" t="inlineStr">
         <is>
-          <t>+$115.41K</t>
+          <t>+$111.54K</t>
         </is>
       </c>
       <c r="G82" s="6" t="inlineStr">
         <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H82" s="6" t="inlineStr"/>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H82" s="6" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
     </row>
     <row r="83">
-      <c r="A83" s="6" t="inlineStr">
+      <c r="A83" s="3" t="inlineStr">
         <is>
           <t>NQ</t>
         </is>
       </c>
-      <c r="B83" s="5" t="n">
-        <v>29552.98</v>
-      </c>
-      <c r="C83" s="5" t="n">
-        <v>29730</v>
-      </c>
-      <c r="D83" s="6" t="inlineStr">
+      <c r="B83" s="2" t="n">
+        <v>29792.98</v>
+      </c>
+      <c r="C83" s="2" t="n">
+        <v>29970</v>
+      </c>
+      <c r="D83" s="3" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="E83" s="7" t="inlineStr">
-        <is>
-          <t>-$113.33K</t>
-        </is>
-      </c>
-      <c r="F83" s="6" t="inlineStr">
-        <is>
-          <t>+$113.33K</t>
-        </is>
-      </c>
-      <c r="G83" s="6" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H83" s="6" t="inlineStr">
-        <is>
-          <t>valley</t>
+      <c r="E83" s="9" t="inlineStr">
+        <is>
+          <t>+$74.56K</t>
+        </is>
+      </c>
+      <c r="F83" s="3" t="inlineStr">
+        <is>
+          <t>+$86.49K</t>
+        </is>
+      </c>
+      <c r="G83" s="3" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H83" s="3" t="inlineStr">
+        <is>
+          <t>peak</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="6" t="inlineStr">
         <is>
+          <t>GC</t>
+        </is>
+      </c>
+      <c r="B84" s="5" t="n">
+        <v>4241.96</v>
+      </c>
+      <c r="C84" s="5" t="n">
+        <v>89.5</v>
+      </c>
+      <c r="D84" s="6" t="inlineStr">
+        <is>
+          <t>GDX</t>
+        </is>
+      </c>
+      <c r="E84" s="8" t="inlineStr">
+        <is>
+          <t>+$37.20K</t>
+        </is>
+      </c>
+      <c r="F84" s="6" t="inlineStr">
+        <is>
+          <t>+$78.91K</t>
+        </is>
+      </c>
+      <c r="G84" s="6" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H84" s="6" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="6" t="inlineStr">
+        <is>
           <t>NQ</t>
         </is>
       </c>
-      <c r="B84" s="5" t="n">
-        <v>29732.98</v>
-      </c>
-      <c r="C84" s="5" t="n">
-        <v>29910</v>
-      </c>
-      <c r="D84" s="6" t="inlineStr">
+      <c r="B85" s="5" t="n">
+        <v>29702.98</v>
+      </c>
+      <c r="C85" s="5" t="n">
+        <v>29880</v>
+      </c>
+      <c r="D85" s="6" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="E84" s="7" t="inlineStr">
-        <is>
-          <t>-$6.56K</t>
-        </is>
-      </c>
-      <c r="F84" s="6" t="inlineStr">
-        <is>
-          <t>+$111.54K</t>
-        </is>
-      </c>
-      <c r="G84" s="6" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H84" s="6" t="inlineStr">
-        <is>
-          <t>valley</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="3" t="inlineStr">
-        <is>
-          <t>NQ</t>
-        </is>
-      </c>
-      <c r="B85" s="2" t="n">
-        <v>29792.98</v>
-      </c>
-      <c r="C85" s="2" t="n">
-        <v>29970</v>
-      </c>
-      <c r="D85" s="3" t="inlineStr">
-        <is>
-          <t>NDX</t>
-        </is>
-      </c>
       <c r="E85" s="8" t="inlineStr">
         <is>
-          <t>+$74.56K</t>
-        </is>
-      </c>
-      <c r="F85" s="3" t="inlineStr">
-        <is>
-          <t>+$86.49K</t>
-        </is>
-      </c>
-      <c r="G85" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H85" s="3" t="inlineStr">
+          <t>+$49.21K</t>
+        </is>
+      </c>
+      <c r="F85" s="6" t="inlineStr">
+        <is>
+          <t>+$75.45K</t>
+        </is>
+      </c>
+      <c r="G85" s="6" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H85" s="6" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
@@ -7102,28 +7020,28 @@
     <row r="86">
       <c r="A86" s="6" t="inlineStr">
         <is>
-          <t>GC</t>
+          <t>NQ</t>
         </is>
       </c>
       <c r="B86" s="5" t="n">
-        <v>4241.96</v>
+        <v>29482.98</v>
       </c>
       <c r="C86" s="5" t="n">
-        <v>89.5</v>
+        <v>29660</v>
       </c>
       <c r="D86" s="6" t="inlineStr">
         <is>
-          <t>GDX</t>
-        </is>
-      </c>
-      <c r="E86" s="9" t="inlineStr">
-        <is>
-          <t>+$37.20K</t>
+          <t>NDX</t>
+        </is>
+      </c>
+      <c r="E86" s="7" t="inlineStr">
+        <is>
+          <t>-$56.66K</t>
         </is>
       </c>
       <c r="F86" s="6" t="inlineStr">
         <is>
-          <t>+$78.91K</t>
+          <t>+$74.56K</t>
         </is>
       </c>
       <c r="G86" s="6" t="inlineStr">
@@ -7140,28 +7058,28 @@
     <row r="87">
       <c r="A87" s="6" t="inlineStr">
         <is>
-          <t>NQ</t>
+          <t>GC</t>
         </is>
       </c>
       <c r="B87" s="5" t="n">
-        <v>29702.98</v>
+        <v>4384.15</v>
       </c>
       <c r="C87" s="5" t="n">
-        <v>29880</v>
+        <v>92.5</v>
       </c>
       <c r="D87" s="6" t="inlineStr">
         <is>
-          <t>NDX</t>
-        </is>
-      </c>
-      <c r="E87" s="9" t="inlineStr">
-        <is>
-          <t>+$49.21K</t>
+          <t>GDX</t>
+        </is>
+      </c>
+      <c r="E87" s="8" t="inlineStr">
+        <is>
+          <t>+$50.95K</t>
         </is>
       </c>
       <c r="F87" s="6" t="inlineStr">
         <is>
-          <t>+$75.45K</t>
+          <t>+$70.79K</t>
         </is>
       </c>
       <c r="G87" s="6" t="inlineStr">
@@ -7171,7 +7089,7 @@
       </c>
       <c r="H87" s="6" t="inlineStr">
         <is>
-          <t>peak</t>
+          <t>valley</t>
         </is>
       </c>
     </row>
@@ -7182,24 +7100,24 @@
         </is>
       </c>
       <c r="B88" s="5" t="n">
-        <v>29482.98</v>
+        <v>29742.98</v>
       </c>
       <c r="C88" s="5" t="n">
-        <v>29660</v>
+        <v>29920</v>
       </c>
       <c r="D88" s="6" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="E88" s="7" t="inlineStr">
-        <is>
-          <t>-$56.66K</t>
+      <c r="E88" s="8" t="inlineStr">
+        <is>
+          <t>+$45.93K</t>
         </is>
       </c>
       <c r="F88" s="6" t="inlineStr">
         <is>
-          <t>+$74.56K</t>
+          <t>+$65.61K</t>
         </is>
       </c>
       <c r="G88" s="6" t="inlineStr">
@@ -7209,47 +7127,43 @@
       </c>
       <c r="H88" s="6" t="inlineStr">
         <is>
-          <t>valley</t>
+          <t>peak</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="6" t="inlineStr">
         <is>
-          <t>GC</t>
+          <t>NQ</t>
         </is>
       </c>
       <c r="B89" s="5" t="n">
-        <v>4384.15</v>
+        <v>29592.98</v>
       </c>
       <c r="C89" s="5" t="n">
-        <v>92.5</v>
+        <v>29770</v>
       </c>
       <c r="D89" s="6" t="inlineStr">
         <is>
-          <t>GDX</t>
-        </is>
-      </c>
-      <c r="E89" s="9" t="inlineStr">
-        <is>
-          <t>+$50.95K</t>
+          <t>NDX</t>
+        </is>
+      </c>
+      <c r="E89" s="7" t="inlineStr">
+        <is>
+          <t>-$42.65K</t>
         </is>
       </c>
       <c r="F89" s="6" t="inlineStr">
         <is>
-          <t>+$70.79K</t>
+          <t>+$62.33K</t>
         </is>
       </c>
       <c r="G89" s="6" t="inlineStr">
         <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H89" s="6" t="inlineStr">
-        <is>
-          <t>valley</t>
-        </is>
-      </c>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H89" s="6" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="6" t="inlineStr">
@@ -7258,26 +7172,26 @@
         </is>
       </c>
       <c r="B90" s="5" t="n">
-        <v>29742.98</v>
+        <v>29747.98</v>
       </c>
       <c r="C90" s="5" t="n">
-        <v>29920</v>
+        <v>29925</v>
       </c>
       <c r="D90" s="6" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="E90" s="9" t="inlineStr">
+      <c r="E90" s="7" t="inlineStr">
+        <is>
+          <t>-$6.56K</t>
+        </is>
+      </c>
+      <c r="F90" s="6" t="inlineStr">
         <is>
           <t>+$45.93K</t>
         </is>
       </c>
-      <c r="F90" s="6" t="inlineStr">
-        <is>
-          <t>+$65.61K</t>
-        </is>
-      </c>
       <c r="G90" s="6" t="inlineStr">
         <is>
           <t>Net</t>
@@ -7285,7 +7199,7 @@
       </c>
       <c r="H90" s="6" t="inlineStr">
         <is>
-          <t>peak</t>
+          <t>valley</t>
         </is>
       </c>
     </row>
@@ -7296,32 +7210,36 @@
         </is>
       </c>
       <c r="B91" s="5" t="n">
-        <v>29592.98</v>
+        <v>29797.98</v>
       </c>
       <c r="C91" s="5" t="n">
-        <v>29770</v>
+        <v>29975</v>
       </c>
       <c r="D91" s="6" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="E91" s="7" t="inlineStr">
-        <is>
-          <t>-$42.65K</t>
+      <c r="E91" s="8" t="inlineStr">
+        <is>
+          <t>+$26.84K</t>
         </is>
       </c>
       <c r="F91" s="6" t="inlineStr">
         <is>
-          <t>+$62.33K</t>
+          <t>+$44.73K</t>
         </is>
       </c>
       <c r="G91" s="6" t="inlineStr">
         <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H91" s="6" t="inlineStr"/>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H91" s="6" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="6" t="inlineStr">
@@ -7330,24 +7248,24 @@
         </is>
       </c>
       <c r="B92" s="5" t="n">
-        <v>29747.98</v>
+        <v>29812.98</v>
       </c>
       <c r="C92" s="5" t="n">
-        <v>29925</v>
+        <v>29990</v>
       </c>
       <c r="D92" s="6" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="E92" s="7" t="inlineStr">
-        <is>
-          <t>-$6.56K</t>
+      <c r="E92" s="8" t="inlineStr">
+        <is>
+          <t>+$32.80K</t>
         </is>
       </c>
       <c r="F92" s="6" t="inlineStr">
         <is>
-          <t>+$45.93K</t>
+          <t>+$38.77K</t>
         </is>
       </c>
       <c r="G92" s="6" t="inlineStr">
@@ -7368,24 +7286,24 @@
         </is>
       </c>
       <c r="B93" s="5" t="n">
-        <v>29797.98</v>
+        <v>29532.98</v>
       </c>
       <c r="C93" s="5" t="n">
-        <v>29975</v>
+        <v>29710</v>
       </c>
       <c r="D93" s="6" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="E93" s="9" t="inlineStr">
-        <is>
-          <t>+$26.84K</t>
+      <c r="E93" s="8" t="inlineStr">
+        <is>
+          <t>+$11.93K</t>
         </is>
       </c>
       <c r="F93" s="6" t="inlineStr">
         <is>
-          <t>+$44.73K</t>
+          <t>+$35.79K</t>
         </is>
       </c>
       <c r="G93" s="6" t="inlineStr">
@@ -7395,7 +7313,7 @@
       </c>
       <c r="H93" s="6" t="inlineStr">
         <is>
-          <t>valley</t>
+          <t>peak</t>
         </is>
       </c>
     </row>
@@ -7406,24 +7324,24 @@
         </is>
       </c>
       <c r="B94" s="5" t="n">
-        <v>29812.98</v>
+        <v>29597.98</v>
       </c>
       <c r="C94" s="5" t="n">
-        <v>29990</v>
+        <v>29775</v>
       </c>
       <c r="D94" s="6" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="E94" s="9" t="inlineStr">
-        <is>
-          <t>+$32.80K</t>
+      <c r="E94" s="7" t="inlineStr">
+        <is>
+          <t>-$19.68K</t>
         </is>
       </c>
       <c r="F94" s="6" t="inlineStr">
         <is>
-          <t>+$38.77K</t>
+          <t>+$26.24K</t>
         </is>
       </c>
       <c r="G94" s="6" t="inlineStr">
@@ -7433,7 +7351,7 @@
       </c>
       <c r="H94" s="6" t="inlineStr">
         <is>
-          <t>valley</t>
+          <t>peak</t>
         </is>
       </c>
     </row>
@@ -7444,24 +7362,24 @@
         </is>
       </c>
       <c r="B95" s="5" t="n">
-        <v>29532.98</v>
+        <v>29492.98</v>
       </c>
       <c r="C95" s="5" t="n">
-        <v>29710</v>
+        <v>29670</v>
       </c>
       <c r="D95" s="6" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="E95" s="9" t="inlineStr">
-        <is>
-          <t>+$11.93K</t>
+      <c r="E95" s="7" t="inlineStr">
+        <is>
+          <t>-$5.96K</t>
         </is>
       </c>
       <c r="F95" s="6" t="inlineStr">
         <is>
-          <t>+$35.79K</t>
+          <t>+$17.89K</t>
         </is>
       </c>
       <c r="G95" s="6" t="inlineStr">
@@ -7482,24 +7400,24 @@
         </is>
       </c>
       <c r="B96" s="5" t="n">
-        <v>29597.98</v>
+        <v>29782.98</v>
       </c>
       <c r="C96" s="5" t="n">
-        <v>29775</v>
+        <v>29960</v>
       </c>
       <c r="D96" s="6" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="E96" s="7" t="inlineStr">
-        <is>
-          <t>-$19.68K</t>
+      <c r="E96" s="8" t="inlineStr">
+        <is>
+          <t>+$11.93K</t>
         </is>
       </c>
       <c r="F96" s="6" t="inlineStr">
         <is>
-          <t>+$26.24K</t>
+          <t>+$11.93K</t>
         </is>
       </c>
       <c r="G96" s="6" t="inlineStr">
@@ -7509,88 +7427,12 @@
       </c>
       <c r="H96" s="6" t="inlineStr">
         <is>
-          <t>peak</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="6" t="inlineStr">
-        <is>
-          <t>NQ</t>
-        </is>
-      </c>
-      <c r="B97" s="5" t="n">
-        <v>29492.98</v>
-      </c>
-      <c r="C97" s="5" t="n">
-        <v>29670</v>
-      </c>
-      <c r="D97" s="6" t="inlineStr">
-        <is>
-          <t>NDX</t>
-        </is>
-      </c>
-      <c r="E97" s="7" t="inlineStr">
-        <is>
-          <t>-$5.96K</t>
-        </is>
-      </c>
-      <c r="F97" s="6" t="inlineStr">
-        <is>
-          <t>+$17.89K</t>
-        </is>
-      </c>
-      <c r="G97" s="6" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H97" s="6" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="6" t="inlineStr">
-        <is>
-          <t>NQ</t>
-        </is>
-      </c>
-      <c r="B98" s="5" t="n">
-        <v>29782.98</v>
-      </c>
-      <c r="C98" s="5" t="n">
-        <v>29960</v>
-      </c>
-      <c r="D98" s="6" t="inlineStr">
-        <is>
-          <t>NDX</t>
-        </is>
-      </c>
-      <c r="E98" s="9" t="inlineStr">
-        <is>
-          <t>+$11.93K</t>
-        </is>
-      </c>
-      <c r="F98" s="6" t="inlineStr">
-        <is>
-          <t>+$11.93K</t>
-        </is>
-      </c>
-      <c r="G98" s="6" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H98" s="6" t="inlineStr">
-        <is>
           <t>valley</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H98"/>
+  <autoFilter ref="A1:H96"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>